--- a/part1_data_cleaning/data/cleaned_orders.xlsx
+++ b/part1_data_cleaning/data/cleaned_orders.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\part1_data_cleaning\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\part1_data_cleaning\part1_data_cleaning\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="7050" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="7050"/>
   </bookViews>
   <sheets>
-    <sheet name="raw_orders" sheetId="1" r:id="rId1"/>
+    <sheet name="cleaned_orders" sheetId="1" r:id="rId1"/>
     <sheet name="business_rules" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">raw_orders!$P$1:$P$933</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cleaned_orders!$P$1:$P$933</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
@@ -8450,7 +8450,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -8680,7 +8680,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AD933"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="3" width="16" style="6" customWidth="1"/>
@@ -8693,7 +8693,7 @@
     <col min="29" max="29" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="27.95" customHeight="1">
+    <row r="1" spans="1:30" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8785,7 +8785,7 @@
         <v>2804</v>
       </c>
     </row>
-    <row r="2" spans="1:30">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>21</v>
       </c>
@@ -8881,7 +8881,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>34</v>
       </c>
@@ -8977,7 +8977,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>45</v>
       </c>
@@ -9072,7 +9072,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>51</v>
       </c>
@@ -9167,7 +9167,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>60</v>
       </c>
@@ -9262,7 +9262,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>69</v>
       </c>
@@ -9357,7 +9357,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>77</v>
       </c>
@@ -9452,7 +9452,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>82</v>
       </c>
@@ -9547,7 +9547,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>87</v>
       </c>
@@ -9642,7 +9642,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="11" spans="1:30">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>93</v>
       </c>
@@ -9737,7 +9737,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="12" spans="1:30">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>97</v>
       </c>
@@ -9832,7 +9832,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>104</v>
       </c>
@@ -9927,7 +9927,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="14" spans="1:30">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>107</v>
       </c>
@@ -10022,7 +10022,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="15" spans="1:30">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>112</v>
       </c>
@@ -10117,7 +10117,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="16" spans="1:30">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>116</v>
       </c>
@@ -10212,7 +10212,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="17" spans="1:30">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>120</v>
       </c>
@@ -10307,7 +10307,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="18" spans="1:30">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>126</v>
       </c>
@@ -10402,7 +10402,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="19" spans="1:30">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>130</v>
       </c>
@@ -10497,7 +10497,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="20" spans="1:30">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>134</v>
       </c>
@@ -10592,7 +10592,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="21" spans="1:30">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>139</v>
       </c>
@@ -10687,7 +10687,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="22" spans="1:30">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>143</v>
       </c>
@@ -10782,7 +10782,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="23" spans="1:30">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>148</v>
       </c>
@@ -10877,7 +10877,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="24" spans="1:30">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>151</v>
       </c>
@@ -10972,7 +10972,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="25" spans="1:30">
+    <row r="25" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>156</v>
       </c>
@@ -11067,7 +11067,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="26" spans="1:30">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>160</v>
       </c>
@@ -11162,7 +11162,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="27" spans="1:30">
+    <row r="27" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>164</v>
       </c>
@@ -11257,7 +11257,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="28" spans="1:30">
+    <row r="28" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>169</v>
       </c>
@@ -11352,7 +11352,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="29" spans="1:30">
+    <row r="29" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>173</v>
       </c>
@@ -11447,7 +11447,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="30" spans="1:30">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>178</v>
       </c>
@@ -11542,7 +11542,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="31" spans="1:30">
+    <row r="31" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>183</v>
       </c>
@@ -11637,7 +11637,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="32" spans="1:30">
+    <row r="32" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>188</v>
       </c>
@@ -11732,7 +11732,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="33" spans="1:30">
+    <row r="33" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>193</v>
       </c>
@@ -11827,7 +11827,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="34" spans="1:30">
+    <row r="34" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>196</v>
       </c>
@@ -11922,7 +11922,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="35" spans="1:30">
+    <row r="35" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>199</v>
       </c>
@@ -12017,7 +12017,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="36" spans="1:30">
+    <row r="36" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>202</v>
       </c>
@@ -12112,7 +12112,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="37" spans="1:30">
+    <row r="37" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>205</v>
       </c>
@@ -12207,7 +12207,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="38" spans="1:30">
+    <row r="38" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>208</v>
       </c>
@@ -12302,7 +12302,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="39" spans="1:30">
+    <row r="39" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>211</v>
       </c>
@@ -12397,7 +12397,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="40" spans="1:30">
+    <row r="40" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>214</v>
       </c>
@@ -12492,7 +12492,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="41" spans="1:30">
+    <row r="41" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>217</v>
       </c>
@@ -12587,7 +12587,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="42" spans="1:30">
+    <row r="42" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>220</v>
       </c>
@@ -12682,7 +12682,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="43" spans="1:30">
+    <row r="43" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>223</v>
       </c>
@@ -12777,7 +12777,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="44" spans="1:30">
+    <row r="44" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>226</v>
       </c>
@@ -12872,7 +12872,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="45" spans="1:30">
+    <row r="45" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>231</v>
       </c>
@@ -12967,7 +12967,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="46" spans="1:30">
+    <row r="46" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
         <v>234</v>
       </c>
@@ -13062,7 +13062,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="47" spans="1:30">
+    <row r="47" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>239</v>
       </c>
@@ -13157,7 +13157,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="48" spans="1:30">
+    <row r="48" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
         <v>242</v>
       </c>
@@ -13252,7 +13252,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="49" spans="1:30">
+    <row r="49" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>245</v>
       </c>
@@ -13347,7 +13347,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="50" spans="1:30">
+    <row r="50" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>250</v>
       </c>
@@ -13442,7 +13442,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="51" spans="1:30">
+    <row r="51" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>253</v>
       </c>
@@ -13537,7 +13537,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="52" spans="1:30">
+    <row r="52" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
         <v>256</v>
       </c>
@@ -13632,7 +13632,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="53" spans="1:30">
+    <row r="53" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>259</v>
       </c>
@@ -13727,7 +13727,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="54" spans="1:30">
+    <row r="54" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
         <v>262</v>
       </c>
@@ -13822,7 +13822,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="55" spans="1:30">
+    <row r="55" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>266</v>
       </c>
@@ -13917,7 +13917,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="56" spans="1:30">
+    <row r="56" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
         <v>269</v>
       </c>
@@ -14012,7 +14012,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="57" spans="1:30">
+    <row r="57" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
         <v>272</v>
       </c>
@@ -14107,7 +14107,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="58" spans="1:30">
+    <row r="58" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
         <v>276</v>
       </c>
@@ -14202,7 +14202,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="59" spans="1:30">
+    <row r="59" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>279</v>
       </c>
@@ -14297,7 +14297,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="60" spans="1:30">
+    <row r="60" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
         <v>282</v>
       </c>
@@ -14392,7 +14392,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="61" spans="1:30">
+    <row r="61" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
         <v>285</v>
       </c>
@@ -14487,7 +14487,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="62" spans="1:30">
+    <row r="62" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>288</v>
       </c>
@@ -14582,7 +14582,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="63" spans="1:30">
+    <row r="63" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
         <v>291</v>
       </c>
@@ -14677,7 +14677,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="64" spans="1:30">
+    <row r="64" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
         <v>294</v>
       </c>
@@ -14772,7 +14772,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="65" spans="1:30">
+    <row r="65" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>297</v>
       </c>
@@ -14867,7 +14867,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="66" spans="1:30">
+    <row r="66" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
         <v>300</v>
       </c>
@@ -14962,7 +14962,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="67" spans="1:30">
+    <row r="67" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
         <v>303</v>
       </c>
@@ -15058,7 +15058,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="68" spans="1:30">
+    <row r="68" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
         <v>306</v>
       </c>
@@ -15153,7 +15153,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="69" spans="1:30">
+    <row r="69" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
         <v>309</v>
       </c>
@@ -15248,7 +15248,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="70" spans="1:30">
+    <row r="70" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
         <v>312</v>
       </c>
@@ -15343,7 +15343,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="71" spans="1:30">
+    <row r="71" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
         <v>315</v>
       </c>
@@ -15438,7 +15438,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="72" spans="1:30">
+    <row r="72" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
         <v>318</v>
       </c>
@@ -15533,7 +15533,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="73" spans="1:30">
+    <row r="73" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
         <v>321</v>
       </c>
@@ -15628,7 +15628,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="74" spans="1:30">
+    <row r="74" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
         <v>324</v>
       </c>
@@ -15723,7 +15723,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="75" spans="1:30">
+    <row r="75" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
         <v>327</v>
       </c>
@@ -15818,7 +15818,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="76" spans="1:30">
+    <row r="76" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
         <v>330</v>
       </c>
@@ -15913,7 +15913,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="77" spans="1:30">
+    <row r="77" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
         <v>333</v>
       </c>
@@ -16008,7 +16008,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="78" spans="1:30">
+    <row r="78" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
         <v>336</v>
       </c>
@@ -16103,7 +16103,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="79" spans="1:30">
+    <row r="79" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
         <v>339</v>
       </c>
@@ -16198,7 +16198,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="80" spans="1:30">
+    <row r="80" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
         <v>342</v>
       </c>
@@ -16293,7 +16293,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="81" spans="1:30">
+    <row r="81" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
         <v>345</v>
       </c>
@@ -16388,7 +16388,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="82" spans="1:30">
+    <row r="82" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
         <v>348</v>
       </c>
@@ -16483,7 +16483,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="83" spans="1:30">
+    <row r="83" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
         <v>353</v>
       </c>
@@ -16578,7 +16578,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="84" spans="1:30">
+    <row r="84" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
         <v>356</v>
       </c>
@@ -16673,7 +16673,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="85" spans="1:30">
+    <row r="85" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
         <v>359</v>
       </c>
@@ -16768,7 +16768,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="86" spans="1:30">
+    <row r="86" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
         <v>362</v>
       </c>
@@ -16863,7 +16863,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="87" spans="1:30">
+    <row r="87" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
         <v>365</v>
       </c>
@@ -16958,7 +16958,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="88" spans="1:30">
+    <row r="88" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
         <v>368</v>
       </c>
@@ -17053,7 +17053,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="89" spans="1:30">
+    <row r="89" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
         <v>371</v>
       </c>
@@ -17148,7 +17148,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="90" spans="1:30">
+    <row r="90" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
         <v>374</v>
       </c>
@@ -17243,7 +17243,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="91" spans="1:30">
+    <row r="91" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
         <v>377</v>
       </c>
@@ -17338,7 +17338,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="92" spans="1:30">
+    <row r="92" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
         <v>380</v>
       </c>
@@ -17433,7 +17433,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="93" spans="1:30">
+    <row r="93" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
         <v>383</v>
       </c>
@@ -17528,7 +17528,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="94" spans="1:30">
+    <row r="94" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
         <v>386</v>
       </c>
@@ -17623,7 +17623,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="95" spans="1:30">
+    <row r="95" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
         <v>389</v>
       </c>
@@ -17718,7 +17718,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="96" spans="1:30">
+    <row r="96" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
         <v>392</v>
       </c>
@@ -17813,7 +17813,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="97" spans="1:30">
+    <row r="97" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
         <v>395</v>
       </c>
@@ -17908,7 +17908,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="98" spans="1:30">
+    <row r="98" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
         <v>398</v>
       </c>
@@ -18003,7 +18003,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="99" spans="1:30">
+    <row r="99" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
         <v>401</v>
       </c>
@@ -18098,7 +18098,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="100" spans="1:30">
+    <row r="100" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
         <v>404</v>
       </c>
@@ -18193,7 +18193,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="101" spans="1:30">
+    <row r="101" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
         <v>407</v>
       </c>
@@ -18288,7 +18288,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="102" spans="1:30">
+    <row r="102" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
         <v>410</v>
       </c>
@@ -18383,7 +18383,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="103" spans="1:30">
+    <row r="103" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
         <v>413</v>
       </c>
@@ -18478,7 +18478,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="104" spans="1:30">
+    <row r="104" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
         <v>416</v>
       </c>
@@ -18573,7 +18573,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="105" spans="1:30">
+    <row r="105" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
         <v>419</v>
       </c>
@@ -18668,7 +18668,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="106" spans="1:30">
+    <row r="106" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
         <v>422</v>
       </c>
@@ -18763,7 +18763,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="107" spans="1:30">
+    <row r="107" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
         <v>425</v>
       </c>
@@ -18858,7 +18858,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="108" spans="1:30">
+    <row r="108" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
         <v>428</v>
       </c>
@@ -18953,7 +18953,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="109" spans="1:30">
+    <row r="109" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
         <v>431</v>
       </c>
@@ -19048,7 +19048,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="110" spans="1:30">
+    <row r="110" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
         <v>434</v>
       </c>
@@ -19143,7 +19143,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="111" spans="1:30">
+    <row r="111" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
         <v>437</v>
       </c>
@@ -19238,7 +19238,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="112" spans="1:30">
+    <row r="112" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
         <v>440</v>
       </c>
@@ -19333,7 +19333,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="113" spans="1:30">
+    <row r="113" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
         <v>443</v>
       </c>
@@ -19428,7 +19428,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="114" spans="1:30">
+    <row r="114" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
         <v>446</v>
       </c>
@@ -19523,7 +19523,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="115" spans="1:30">
+    <row r="115" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
         <v>449</v>
       </c>
@@ -19618,7 +19618,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="116" spans="1:30">
+    <row r="116" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
         <v>451</v>
       </c>
@@ -19713,7 +19713,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="117" spans="1:30">
+    <row r="117" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
         <v>454</v>
       </c>
@@ -19808,7 +19808,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="118" spans="1:30">
+    <row r="118" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
         <v>457</v>
       </c>
@@ -19903,7 +19903,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="119" spans="1:30">
+    <row r="119" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
         <v>460</v>
       </c>
@@ -19998,7 +19998,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="120" spans="1:30">
+    <row r="120" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
         <v>463</v>
       </c>
@@ -20093,7 +20093,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="121" spans="1:30">
+    <row r="121" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
         <v>466</v>
       </c>
@@ -20188,7 +20188,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="122" spans="1:30">
+    <row r="122" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
         <v>469</v>
       </c>
@@ -20283,7 +20283,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="123" spans="1:30">
+    <row r="123" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
         <v>472</v>
       </c>
@@ -20378,7 +20378,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="124" spans="1:30">
+    <row r="124" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
         <v>475</v>
       </c>
@@ -20473,7 +20473,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="125" spans="1:30">
+    <row r="125" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
         <v>478</v>
       </c>
@@ -20568,7 +20568,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="126" spans="1:30">
+    <row r="126" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
         <v>481</v>
       </c>
@@ -20663,7 +20663,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="127" spans="1:30">
+    <row r="127" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
         <v>484</v>
       </c>
@@ -20758,7 +20758,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="128" spans="1:30">
+    <row r="128" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
         <v>487</v>
       </c>
@@ -20853,7 +20853,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="129" spans="1:30">
+    <row r="129" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
         <v>490</v>
       </c>
@@ -20948,7 +20948,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="130" spans="1:30">
+    <row r="130" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A130" s="3" t="s">
         <v>493</v>
       </c>
@@ -21043,7 +21043,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="131" spans="1:30">
+    <row r="131" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="s">
         <v>496</v>
       </c>
@@ -21139,7 +21139,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="132" spans="1:30">
+    <row r="132" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A132" s="3" t="s">
         <v>499</v>
       </c>
@@ -21234,7 +21234,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="133" spans="1:30">
+    <row r="133" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
         <v>502</v>
       </c>
@@ -21329,7 +21329,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="134" spans="1:30">
+    <row r="134" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A134" s="3" t="s">
         <v>505</v>
       </c>
@@ -21424,7 +21424,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="135" spans="1:30">
+    <row r="135" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
         <v>508</v>
       </c>
@@ -21519,7 +21519,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="136" spans="1:30">
+    <row r="136" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="s">
         <v>511</v>
       </c>
@@ -21614,7 +21614,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="137" spans="1:30">
+    <row r="137" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A137" s="3" t="s">
         <v>514</v>
       </c>
@@ -21709,7 +21709,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="138" spans="1:30">
+    <row r="138" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
         <v>517</v>
       </c>
@@ -21804,7 +21804,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="139" spans="1:30">
+    <row r="139" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A139" s="3" t="s">
         <v>520</v>
       </c>
@@ -21899,7 +21899,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="140" spans="1:30">
+    <row r="140" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
         <v>523</v>
       </c>
@@ -21994,7 +21994,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="141" spans="1:30">
+    <row r="141" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
         <v>526</v>
       </c>
@@ -22089,7 +22089,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="142" spans="1:30">
+    <row r="142" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A142" s="3" t="s">
         <v>529</v>
       </c>
@@ -22184,7 +22184,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="143" spans="1:30">
+    <row r="143" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
         <v>532</v>
       </c>
@@ -22279,7 +22279,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="144" spans="1:30">
+    <row r="144" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A144" s="3" t="s">
         <v>535</v>
       </c>
@@ -22374,7 +22374,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="145" spans="1:30">
+    <row r="145" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A145" s="3" t="s">
         <v>538</v>
       </c>
@@ -22469,7 +22469,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="146" spans="1:30">
+    <row r="146" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A146" s="3" t="s">
         <v>541</v>
       </c>
@@ -22564,7 +22564,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="147" spans="1:30">
+    <row r="147" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A147" s="3" t="s">
         <v>544</v>
       </c>
@@ -22659,7 +22659,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="148" spans="1:30">
+    <row r="148" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A148" s="3" t="s">
         <v>547</v>
       </c>
@@ -22754,7 +22754,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="149" spans="1:30">
+    <row r="149" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A149" s="3" t="s">
         <v>550</v>
       </c>
@@ -22849,7 +22849,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="150" spans="1:30">
+    <row r="150" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A150" s="3" t="s">
         <v>553</v>
       </c>
@@ -22944,7 +22944,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="151" spans="1:30">
+    <row r="151" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A151" s="3" t="s">
         <v>556</v>
       </c>
@@ -23039,7 +23039,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="152" spans="1:30">
+    <row r="152" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A152" s="3" t="s">
         <v>559</v>
       </c>
@@ -23134,7 +23134,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="153" spans="1:30">
+    <row r="153" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A153" s="3" t="s">
         <v>562</v>
       </c>
@@ -23229,7 +23229,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="154" spans="1:30">
+    <row r="154" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A154" s="3" t="s">
         <v>565</v>
       </c>
@@ -23324,7 +23324,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="155" spans="1:30">
+    <row r="155" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A155" s="3" t="s">
         <v>568</v>
       </c>
@@ -23419,7 +23419,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="156" spans="1:30">
+    <row r="156" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A156" s="3" t="s">
         <v>571</v>
       </c>
@@ -23514,7 +23514,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="157" spans="1:30">
+    <row r="157" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A157" s="3" t="s">
         <v>573</v>
       </c>
@@ -23609,7 +23609,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="158" spans="1:30">
+    <row r="158" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A158" s="3" t="s">
         <v>576</v>
       </c>
@@ -23704,7 +23704,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="159" spans="1:30">
+    <row r="159" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A159" s="3" t="s">
         <v>579</v>
       </c>
@@ -23799,7 +23799,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="160" spans="1:30">
+    <row r="160" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A160" s="3" t="s">
         <v>582</v>
       </c>
@@ -23894,7 +23894,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="161" spans="1:30">
+    <row r="161" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A161" s="3" t="s">
         <v>585</v>
       </c>
@@ -23989,7 +23989,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="162" spans="1:30">
+    <row r="162" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A162" s="3" t="s">
         <v>588</v>
       </c>
@@ -24084,7 +24084,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="163" spans="1:30">
+    <row r="163" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A163" s="3" t="s">
         <v>591</v>
       </c>
@@ -24179,7 +24179,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="164" spans="1:30">
+    <row r="164" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A164" s="3" t="s">
         <v>594</v>
       </c>
@@ -24274,7 +24274,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="165" spans="1:30">
+    <row r="165" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A165" s="3" t="s">
         <v>597</v>
       </c>
@@ -24369,7 +24369,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="166" spans="1:30">
+    <row r="166" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A166" s="3" t="s">
         <v>600</v>
       </c>
@@ -24464,7 +24464,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="167" spans="1:30">
+    <row r="167" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A167" s="3" t="s">
         <v>603</v>
       </c>
@@ -24559,7 +24559,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="168" spans="1:30">
+    <row r="168" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A168" s="3" t="s">
         <v>606</v>
       </c>
@@ -24654,7 +24654,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="169" spans="1:30">
+    <row r="169" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A169" s="3" t="s">
         <v>609</v>
       </c>
@@ -24749,7 +24749,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="170" spans="1:30">
+    <row r="170" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A170" s="3" t="s">
         <v>612</v>
       </c>
@@ -24844,7 +24844,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="171" spans="1:30">
+    <row r="171" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A171" s="3" t="s">
         <v>615</v>
       </c>
@@ -24939,7 +24939,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="172" spans="1:30">
+    <row r="172" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A172" s="3" t="s">
         <v>618</v>
       </c>
@@ -25034,7 +25034,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="173" spans="1:30">
+    <row r="173" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A173" s="3" t="s">
         <v>621</v>
       </c>
@@ -25129,7 +25129,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="174" spans="1:30">
+    <row r="174" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A174" s="3" t="s">
         <v>624</v>
       </c>
@@ -25224,7 +25224,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="175" spans="1:30">
+    <row r="175" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A175" s="3" t="s">
         <v>627</v>
       </c>
@@ -25319,7 +25319,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="176" spans="1:30">
+    <row r="176" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A176" s="3" t="s">
         <v>630</v>
       </c>
@@ -25414,7 +25414,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="177" spans="1:30">
+    <row r="177" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A177" s="3" t="s">
         <v>633</v>
       </c>
@@ -25509,7 +25509,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="178" spans="1:30">
+    <row r="178" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A178" s="3" t="s">
         <v>636</v>
       </c>
@@ -25604,7 +25604,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="179" spans="1:30">
+    <row r="179" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A179" s="3" t="s">
         <v>639</v>
       </c>
@@ -25699,7 +25699,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="180" spans="1:30">
+    <row r="180" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A180" s="3" t="s">
         <v>642</v>
       </c>
@@ -25794,7 +25794,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="181" spans="1:30">
+    <row r="181" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A181" s="3" t="s">
         <v>645</v>
       </c>
@@ -25889,7 +25889,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="182" spans="1:30">
+    <row r="182" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A182" s="3" t="s">
         <v>648</v>
       </c>
@@ -25984,7 +25984,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="183" spans="1:30">
+    <row r="183" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A183" s="3" t="s">
         <v>651</v>
       </c>
@@ -26079,7 +26079,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="184" spans="1:30">
+    <row r="184" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A184" s="3" t="s">
         <v>654</v>
       </c>
@@ -26174,7 +26174,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="185" spans="1:30">
+    <row r="185" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A185" s="3" t="s">
         <v>657</v>
       </c>
@@ -26269,7 +26269,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="186" spans="1:30">
+    <row r="186" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A186" s="3" t="s">
         <v>660</v>
       </c>
@@ -26364,7 +26364,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="187" spans="1:30">
+    <row r="187" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A187" s="3" t="s">
         <v>663</v>
       </c>
@@ -26459,7 +26459,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="188" spans="1:30">
+    <row r="188" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A188" s="3" t="s">
         <v>666</v>
       </c>
@@ -26554,7 +26554,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="189" spans="1:30">
+    <row r="189" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A189" s="3" t="s">
         <v>668</v>
       </c>
@@ -26649,7 +26649,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="190" spans="1:30">
+    <row r="190" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A190" s="3" t="s">
         <v>671</v>
       </c>
@@ -26744,7 +26744,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="191" spans="1:30">
+    <row r="191" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A191" s="3" t="s">
         <v>674</v>
       </c>
@@ -26839,7 +26839,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="192" spans="1:30">
+    <row r="192" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A192" s="3" t="s">
         <v>677</v>
       </c>
@@ -26934,7 +26934,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="193" spans="1:30">
+    <row r="193" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A193" s="3" t="s">
         <v>680</v>
       </c>
@@ -27029,7 +27029,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="194" spans="1:30">
+    <row r="194" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A194" s="3" t="s">
         <v>683</v>
       </c>
@@ -27124,7 +27124,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="195" spans="1:30">
+    <row r="195" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A195" s="3" t="s">
         <v>686</v>
       </c>
@@ -27220,7 +27220,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="196" spans="1:30">
+    <row r="196" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A196" s="3" t="s">
         <v>689</v>
       </c>
@@ -27315,7 +27315,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="197" spans="1:30">
+    <row r="197" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A197" s="3" t="s">
         <v>692</v>
       </c>
@@ -27410,7 +27410,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="198" spans="1:30">
+    <row r="198" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A198" s="3" t="s">
         <v>695</v>
       </c>
@@ -27505,7 +27505,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="199" spans="1:30">
+    <row r="199" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A199" s="3" t="s">
         <v>698</v>
       </c>
@@ -27600,7 +27600,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="200" spans="1:30">
+    <row r="200" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A200" s="3" t="s">
         <v>700</v>
       </c>
@@ -27695,7 +27695,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="201" spans="1:30">
+    <row r="201" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A201" s="3" t="s">
         <v>703</v>
       </c>
@@ -27790,7 +27790,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="202" spans="1:30">
+    <row r="202" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A202" s="3" t="s">
         <v>706</v>
       </c>
@@ -27885,7 +27885,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="203" spans="1:30">
+    <row r="203" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A203" s="3" t="s">
         <v>709</v>
       </c>
@@ -27980,7 +27980,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="204" spans="1:30">
+    <row r="204" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A204" s="3" t="s">
         <v>712</v>
       </c>
@@ -28075,7 +28075,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="205" spans="1:30">
+    <row r="205" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A205" s="3" t="s">
         <v>715</v>
       </c>
@@ -28170,7 +28170,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="206" spans="1:30">
+    <row r="206" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A206" s="3" t="s">
         <v>718</v>
       </c>
@@ -28265,7 +28265,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="207" spans="1:30">
+    <row r="207" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A207" s="3" t="s">
         <v>721</v>
       </c>
@@ -28360,7 +28360,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="208" spans="1:30">
+    <row r="208" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A208" s="3" t="s">
         <v>724</v>
       </c>
@@ -28455,7 +28455,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="209" spans="1:30">
+    <row r="209" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A209" s="3" t="s">
         <v>727</v>
       </c>
@@ -28550,7 +28550,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="210" spans="1:30">
+    <row r="210" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A210" s="3" t="s">
         <v>730</v>
       </c>
@@ -28645,7 +28645,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="211" spans="1:30">
+    <row r="211" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A211" s="3" t="s">
         <v>733</v>
       </c>
@@ -28740,7 +28740,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="212" spans="1:30">
+    <row r="212" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A212" s="3" t="s">
         <v>736</v>
       </c>
@@ -28835,7 +28835,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="213" spans="1:30">
+    <row r="213" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A213" s="3" t="s">
         <v>739</v>
       </c>
@@ -28930,7 +28930,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="214" spans="1:30">
+    <row r="214" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A214" s="3" t="s">
         <v>742</v>
       </c>
@@ -29025,7 +29025,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="215" spans="1:30">
+    <row r="215" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A215" s="3" t="s">
         <v>745</v>
       </c>
@@ -29120,7 +29120,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="216" spans="1:30">
+    <row r="216" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A216" s="3" t="s">
         <v>748</v>
       </c>
@@ -29215,7 +29215,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="217" spans="1:30">
+    <row r="217" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A217" s="3" t="s">
         <v>751</v>
       </c>
@@ -29310,7 +29310,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="218" spans="1:30">
+    <row r="218" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A218" s="3" t="s">
         <v>754</v>
       </c>
@@ -29405,7 +29405,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="219" spans="1:30">
+    <row r="219" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A219" s="3" t="s">
         <v>757</v>
       </c>
@@ -29500,7 +29500,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="220" spans="1:30">
+    <row r="220" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A220" s="3" t="s">
         <v>760</v>
       </c>
@@ -29595,7 +29595,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="221" spans="1:30">
+    <row r="221" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A221" s="3" t="s">
         <v>763</v>
       </c>
@@ -29690,7 +29690,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="222" spans="1:30">
+    <row r="222" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A222" s="3" t="s">
         <v>766</v>
       </c>
@@ -29785,7 +29785,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="223" spans="1:30">
+    <row r="223" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A223" s="3" t="s">
         <v>769</v>
       </c>
@@ -29880,7 +29880,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="224" spans="1:30">
+    <row r="224" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A224" s="3" t="s">
         <v>772</v>
       </c>
@@ -29975,7 +29975,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="225" spans="1:30">
+    <row r="225" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A225" s="3" t="s">
         <v>775</v>
       </c>
@@ -30070,7 +30070,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="226" spans="1:30">
+    <row r="226" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A226" s="3" t="s">
         <v>778</v>
       </c>
@@ -30165,7 +30165,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="227" spans="1:30">
+    <row r="227" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A227" s="3" t="s">
         <v>781</v>
       </c>
@@ -30260,7 +30260,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="228" spans="1:30">
+    <row r="228" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A228" s="3" t="s">
         <v>784</v>
       </c>
@@ -30355,7 +30355,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="229" spans="1:30">
+    <row r="229" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A229" s="3" t="s">
         <v>787</v>
       </c>
@@ -30450,7 +30450,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="230" spans="1:30">
+    <row r="230" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A230" s="3" t="s">
         <v>790</v>
       </c>
@@ -30545,7 +30545,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="231" spans="1:30">
+    <row r="231" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A231" s="3" t="s">
         <v>793</v>
       </c>
@@ -30640,7 +30640,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="232" spans="1:30">
+    <row r="232" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A232" s="3" t="s">
         <v>796</v>
       </c>
@@ -30735,7 +30735,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="233" spans="1:30">
+    <row r="233" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A233" s="3" t="s">
         <v>799</v>
       </c>
@@ -30830,7 +30830,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="234" spans="1:30">
+    <row r="234" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A234" s="3" t="s">
         <v>802</v>
       </c>
@@ -30925,7 +30925,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="235" spans="1:30">
+    <row r="235" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A235" s="3" t="s">
         <v>805</v>
       </c>
@@ -31020,7 +31020,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="236" spans="1:30">
+    <row r="236" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A236" s="3" t="s">
         <v>808</v>
       </c>
@@ -31115,7 +31115,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="237" spans="1:30">
+    <row r="237" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A237" s="3" t="s">
         <v>811</v>
       </c>
@@ -31210,7 +31210,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="238" spans="1:30">
+    <row r="238" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A238" s="3" t="s">
         <v>814</v>
       </c>
@@ -31305,7 +31305,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="239" spans="1:30">
+    <row r="239" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A239" s="3" t="s">
         <v>817</v>
       </c>
@@ -31400,7 +31400,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="240" spans="1:30">
+    <row r="240" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A240" s="3" t="s">
         <v>820</v>
       </c>
@@ -31495,7 +31495,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="241" spans="1:30">
+    <row r="241" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A241" s="3" t="s">
         <v>823</v>
       </c>
@@ -31590,7 +31590,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="242" spans="1:30">
+    <row r="242" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A242" s="3" t="s">
         <v>826</v>
       </c>
@@ -31685,7 +31685,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="243" spans="1:30">
+    <row r="243" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A243" s="3" t="s">
         <v>829</v>
       </c>
@@ -31780,7 +31780,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="244" spans="1:30">
+    <row r="244" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A244" s="3" t="s">
         <v>832</v>
       </c>
@@ -31875,7 +31875,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="245" spans="1:30">
+    <row r="245" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A245" s="3" t="s">
         <v>835</v>
       </c>
@@ -31970,7 +31970,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="246" spans="1:30">
+    <row r="246" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A246" s="3" t="s">
         <v>838</v>
       </c>
@@ -32065,7 +32065,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="247" spans="1:30">
+    <row r="247" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A247" s="3" t="s">
         <v>841</v>
       </c>
@@ -32160,7 +32160,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="248" spans="1:30">
+    <row r="248" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A248" s="3" t="s">
         <v>844</v>
       </c>
@@ -32255,7 +32255,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="249" spans="1:30">
+    <row r="249" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A249" s="3" t="s">
         <v>847</v>
       </c>
@@ -32350,7 +32350,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="250" spans="1:30">
+    <row r="250" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A250" s="3" t="s">
         <v>850</v>
       </c>
@@ -32445,7 +32445,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="251" spans="1:30">
+    <row r="251" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A251" s="3" t="s">
         <v>853</v>
       </c>
@@ -32540,7 +32540,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="252" spans="1:30">
+    <row r="252" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A252" s="3" t="s">
         <v>856</v>
       </c>
@@ -32635,7 +32635,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="253" spans="1:30">
+    <row r="253" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A253" s="3" t="s">
         <v>859</v>
       </c>
@@ -32730,7 +32730,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="254" spans="1:30">
+    <row r="254" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A254" s="3" t="s">
         <v>862</v>
       </c>
@@ -32825,7 +32825,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="255" spans="1:30">
+    <row r="255" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A255" s="3" t="s">
         <v>865</v>
       </c>
@@ -32920,7 +32920,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="256" spans="1:30">
+    <row r="256" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A256" s="3" t="s">
         <v>868</v>
       </c>
@@ -33015,7 +33015,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="257" spans="1:30">
+    <row r="257" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A257" s="3" t="s">
         <v>871</v>
       </c>
@@ -33110,7 +33110,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="258" spans="1:30">
+    <row r="258" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A258" s="3" t="s">
         <v>874</v>
       </c>
@@ -33205,7 +33205,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="259" spans="1:30">
+    <row r="259" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A259" s="3" t="s">
         <v>877</v>
       </c>
@@ -33301,7 +33301,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="260" spans="1:30">
+    <row r="260" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A260" s="3" t="s">
         <v>880</v>
       </c>
@@ -33396,7 +33396,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="261" spans="1:30">
+    <row r="261" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A261" s="3" t="s">
         <v>883</v>
       </c>
@@ -33491,7 +33491,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="262" spans="1:30">
+    <row r="262" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A262" s="3" t="s">
         <v>886</v>
       </c>
@@ -33586,7 +33586,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="263" spans="1:30">
+    <row r="263" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A263" s="3" t="s">
         <v>889</v>
       </c>
@@ -33681,7 +33681,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="264" spans="1:30">
+    <row r="264" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A264" s="3" t="s">
         <v>892</v>
       </c>
@@ -33776,7 +33776,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="265" spans="1:30">
+    <row r="265" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A265" s="3" t="s">
         <v>894</v>
       </c>
@@ -33871,7 +33871,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="266" spans="1:30">
+    <row r="266" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A266" s="3" t="s">
         <v>897</v>
       </c>
@@ -33966,7 +33966,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="267" spans="1:30">
+    <row r="267" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A267" s="3" t="s">
         <v>900</v>
       </c>
@@ -34061,7 +34061,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="268" spans="1:30">
+    <row r="268" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A268" s="3" t="s">
         <v>903</v>
       </c>
@@ -34156,7 +34156,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="269" spans="1:30">
+    <row r="269" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A269" s="3" t="s">
         <v>906</v>
       </c>
@@ -34251,7 +34251,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="270" spans="1:30">
+    <row r="270" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A270" s="3" t="s">
         <v>909</v>
       </c>
@@ -34346,7 +34346,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="271" spans="1:30">
+    <row r="271" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A271" s="3" t="s">
         <v>912</v>
       </c>
@@ -34441,7 +34441,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="272" spans="1:30">
+    <row r="272" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A272" s="3" t="s">
         <v>915</v>
       </c>
@@ -34536,7 +34536,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="273" spans="1:30">
+    <row r="273" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A273" s="3" t="s">
         <v>918</v>
       </c>
@@ -34631,7 +34631,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="274" spans="1:30">
+    <row r="274" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A274" s="3" t="s">
         <v>921</v>
       </c>
@@ -34726,7 +34726,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="275" spans="1:30">
+    <row r="275" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A275" s="3" t="s">
         <v>924</v>
       </c>
@@ -34821,7 +34821,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="276" spans="1:30">
+    <row r="276" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A276" s="3" t="s">
         <v>927</v>
       </c>
@@ -34916,7 +34916,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="277" spans="1:30">
+    <row r="277" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A277" s="3" t="s">
         <v>930</v>
       </c>
@@ -35011,7 +35011,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="278" spans="1:30">
+    <row r="278" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A278" s="3" t="s">
         <v>933</v>
       </c>
@@ -35106,7 +35106,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="279" spans="1:30">
+    <row r="279" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A279" s="3" t="s">
         <v>936</v>
       </c>
@@ -35201,7 +35201,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="280" spans="1:30">
+    <row r="280" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A280" s="3" t="s">
         <v>938</v>
       </c>
@@ -35296,7 +35296,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="281" spans="1:30">
+    <row r="281" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A281" s="3" t="s">
         <v>941</v>
       </c>
@@ -35391,7 +35391,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="282" spans="1:30">
+    <row r="282" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A282" s="3" t="s">
         <v>944</v>
       </c>
@@ -35486,7 +35486,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="283" spans="1:30">
+    <row r="283" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A283" s="3" t="s">
         <v>947</v>
       </c>
@@ -35581,7 +35581,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="284" spans="1:30">
+    <row r="284" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A284" s="3" t="s">
         <v>950</v>
       </c>
@@ -35676,7 +35676,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="285" spans="1:30">
+    <row r="285" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A285" s="3" t="s">
         <v>953</v>
       </c>
@@ -35771,7 +35771,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="286" spans="1:30">
+    <row r="286" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A286" s="3" t="s">
         <v>956</v>
       </c>
@@ -35866,7 +35866,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="287" spans="1:30">
+    <row r="287" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A287" s="3" t="s">
         <v>959</v>
       </c>
@@ -35961,7 +35961,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="288" spans="1:30">
+    <row r="288" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A288" s="3" t="s">
         <v>962</v>
       </c>
@@ -36056,7 +36056,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="289" spans="1:30">
+    <row r="289" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A289" s="3" t="s">
         <v>965</v>
       </c>
@@ -36151,7 +36151,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="290" spans="1:30">
+    <row r="290" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A290" s="3" t="s">
         <v>968</v>
       </c>
@@ -36246,7 +36246,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="291" spans="1:30">
+    <row r="291" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A291" s="3" t="s">
         <v>971</v>
       </c>
@@ -36341,7 +36341,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="292" spans="1:30">
+    <row r="292" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A292" s="3" t="s">
         <v>974</v>
       </c>
@@ -36436,7 +36436,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="293" spans="1:30">
+    <row r="293" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A293" s="3" t="s">
         <v>977</v>
       </c>
@@ -36531,7 +36531,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="294" spans="1:30">
+    <row r="294" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A294" s="3" t="s">
         <v>980</v>
       </c>
@@ -36626,7 +36626,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="295" spans="1:30">
+    <row r="295" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A295" s="3" t="s">
         <v>983</v>
       </c>
@@ -36721,7 +36721,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="296" spans="1:30">
+    <row r="296" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A296" s="3" t="s">
         <v>986</v>
       </c>
@@ -36816,7 +36816,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="297" spans="1:30">
+    <row r="297" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A297" s="3" t="s">
         <v>989</v>
       </c>
@@ -36911,7 +36911,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="298" spans="1:30">
+    <row r="298" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A298" s="3" t="s">
         <v>992</v>
       </c>
@@ -37006,7 +37006,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="299" spans="1:30">
+    <row r="299" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A299" s="3" t="s">
         <v>995</v>
       </c>
@@ -37101,7 +37101,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="300" spans="1:30">
+    <row r="300" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A300" s="3" t="s">
         <v>998</v>
       </c>
@@ -37196,7 +37196,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="301" spans="1:30">
+    <row r="301" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A301" s="3" t="s">
         <v>1001</v>
       </c>
@@ -37291,7 +37291,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="302" spans="1:30">
+    <row r="302" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A302" s="3" t="s">
         <v>1004</v>
       </c>
@@ -37386,7 +37386,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="303" spans="1:30">
+    <row r="303" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A303" s="3" t="s">
         <v>1007</v>
       </c>
@@ -37481,7 +37481,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="304" spans="1:30">
+    <row r="304" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A304" s="3" t="s">
         <v>1010</v>
       </c>
@@ -37576,7 +37576,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="305" spans="1:30">
+    <row r="305" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A305" s="3" t="s">
         <v>1013</v>
       </c>
@@ -37671,7 +37671,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="306" spans="1:30">
+    <row r="306" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A306" s="3" t="s">
         <v>1016</v>
       </c>
@@ -37766,7 +37766,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="307" spans="1:30">
+    <row r="307" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A307" s="3" t="s">
         <v>1019</v>
       </c>
@@ -37861,7 +37861,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="308" spans="1:30">
+    <row r="308" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A308" s="3" t="s">
         <v>1022</v>
       </c>
@@ -37956,7 +37956,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="309" spans="1:30">
+    <row r="309" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A309" s="3" t="s">
         <v>1025</v>
       </c>
@@ -38051,7 +38051,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="310" spans="1:30">
+    <row r="310" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A310" s="3" t="s">
         <v>1028</v>
       </c>
@@ -38146,7 +38146,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="311" spans="1:30">
+    <row r="311" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A311" s="3" t="s">
         <v>1031</v>
       </c>
@@ -38241,7 +38241,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="312" spans="1:30">
+    <row r="312" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A312" s="3" t="s">
         <v>1034</v>
       </c>
@@ -38336,7 +38336,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="313" spans="1:30">
+    <row r="313" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A313" s="3" t="s">
         <v>1037</v>
       </c>
@@ -38431,7 +38431,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="314" spans="1:30">
+    <row r="314" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A314" s="3" t="s">
         <v>1040</v>
       </c>
@@ -38526,7 +38526,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="315" spans="1:30">
+    <row r="315" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A315" s="3" t="s">
         <v>1043</v>
       </c>
@@ -38621,7 +38621,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="316" spans="1:30">
+    <row r="316" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A316" s="3" t="s">
         <v>1046</v>
       </c>
@@ -38716,7 +38716,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="317" spans="1:30">
+    <row r="317" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A317" s="3" t="s">
         <v>1049</v>
       </c>
@@ -38811,7 +38811,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="318" spans="1:30">
+    <row r="318" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A318" s="3" t="s">
         <v>1052</v>
       </c>
@@ -38906,7 +38906,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="319" spans="1:30">
+    <row r="319" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A319" s="3" t="s">
         <v>1055</v>
       </c>
@@ -39001,7 +39001,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="320" spans="1:30">
+    <row r="320" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A320" s="3" t="s">
         <v>1058</v>
       </c>
@@ -39096,7 +39096,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="321" spans="1:30">
+    <row r="321" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A321" s="3" t="s">
         <v>1061</v>
       </c>
@@ -39191,7 +39191,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="322" spans="1:30">
+    <row r="322" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A322" s="3" t="s">
         <v>1064</v>
       </c>
@@ -39286,7 +39286,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="323" spans="1:30">
+    <row r="323" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A323" s="3" t="s">
         <v>1067</v>
       </c>
@@ -39382,7 +39382,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="324" spans="1:30">
+    <row r="324" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A324" s="3" t="s">
         <v>1070</v>
       </c>
@@ -39477,7 +39477,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="325" spans="1:30">
+    <row r="325" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A325" s="3" t="s">
         <v>1073</v>
       </c>
@@ -39572,7 +39572,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="326" spans="1:30">
+    <row r="326" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A326" s="3" t="s">
         <v>1075</v>
       </c>
@@ -39667,7 +39667,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="327" spans="1:30">
+    <row r="327" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A327" s="3" t="s">
         <v>1078</v>
       </c>
@@ -39762,7 +39762,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="328" spans="1:30">
+    <row r="328" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A328" s="3" t="s">
         <v>1081</v>
       </c>
@@ -39857,7 +39857,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="329" spans="1:30">
+    <row r="329" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A329" s="3" t="s">
         <v>1084</v>
       </c>
@@ -39952,7 +39952,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="330" spans="1:30">
+    <row r="330" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A330" s="3" t="s">
         <v>1087</v>
       </c>
@@ -40047,7 +40047,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="331" spans="1:30">
+    <row r="331" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A331" s="3" t="s">
         <v>1090</v>
       </c>
@@ -40142,7 +40142,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="332" spans="1:30">
+    <row r="332" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A332" s="3" t="s">
         <v>1093</v>
       </c>
@@ -40237,7 +40237,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="333" spans="1:30">
+    <row r="333" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A333" s="3" t="s">
         <v>1096</v>
       </c>
@@ -40332,7 +40332,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="334" spans="1:30">
+    <row r="334" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A334" s="3" t="s">
         <v>1099</v>
       </c>
@@ -40427,7 +40427,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="335" spans="1:30">
+    <row r="335" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A335" s="3" t="s">
         <v>1102</v>
       </c>
@@ -40522,7 +40522,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="336" spans="1:30">
+    <row r="336" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A336" s="3" t="s">
         <v>1105</v>
       </c>
@@ -40617,7 +40617,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="337" spans="1:30">
+    <row r="337" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A337" s="3" t="s">
         <v>1108</v>
       </c>
@@ -40712,7 +40712,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="338" spans="1:30">
+    <row r="338" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A338" s="3" t="s">
         <v>1111</v>
       </c>
@@ -40807,7 +40807,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="339" spans="1:30">
+    <row r="339" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A339" s="3" t="s">
         <v>1113</v>
       </c>
@@ -40902,7 +40902,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="340" spans="1:30">
+    <row r="340" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A340" s="3" t="s">
         <v>1116</v>
       </c>
@@ -40997,7 +40997,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="341" spans="1:30">
+    <row r="341" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A341" s="3" t="s">
         <v>1119</v>
       </c>
@@ -41092,7 +41092,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="342" spans="1:30">
+    <row r="342" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A342" s="3" t="s">
         <v>1122</v>
       </c>
@@ -41187,7 +41187,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="343" spans="1:30">
+    <row r="343" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A343" s="3" t="s">
         <v>1125</v>
       </c>
@@ -41282,7 +41282,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="344" spans="1:30">
+    <row r="344" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A344" s="3" t="s">
         <v>1128</v>
       </c>
@@ -41377,7 +41377,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="345" spans="1:30">
+    <row r="345" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A345" s="3" t="s">
         <v>1131</v>
       </c>
@@ -41472,7 +41472,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="346" spans="1:30">
+    <row r="346" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A346" s="3" t="s">
         <v>1134</v>
       </c>
@@ -41567,7 +41567,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="347" spans="1:30">
+    <row r="347" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A347" s="3" t="s">
         <v>1137</v>
       </c>
@@ -41662,7 +41662,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="348" spans="1:30">
+    <row r="348" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A348" s="3" t="s">
         <v>1140</v>
       </c>
@@ -41757,7 +41757,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="349" spans="1:30">
+    <row r="349" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A349" s="3" t="s">
         <v>1143</v>
       </c>
@@ -41852,7 +41852,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="350" spans="1:30">
+    <row r="350" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A350" s="3" t="s">
         <v>1146</v>
       </c>
@@ -41947,7 +41947,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="351" spans="1:30">
+    <row r="351" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A351" s="3" t="s">
         <v>1149</v>
       </c>
@@ -42042,7 +42042,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="352" spans="1:30">
+    <row r="352" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A352" s="3" t="s">
         <v>1152</v>
       </c>
@@ -42137,7 +42137,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="353" spans="1:30">
+    <row r="353" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A353" s="3" t="s">
         <v>1155</v>
       </c>
@@ -42232,7 +42232,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="354" spans="1:30">
+    <row r="354" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A354" s="3" t="s">
         <v>1158</v>
       </c>
@@ -42327,7 +42327,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="355" spans="1:30">
+    <row r="355" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A355" s="3" t="s">
         <v>1161</v>
       </c>
@@ -42422,7 +42422,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="356" spans="1:30">
+    <row r="356" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A356" s="3" t="s">
         <v>1164</v>
       </c>
@@ -42517,7 +42517,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="357" spans="1:30">
+    <row r="357" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A357" s="3" t="s">
         <v>1167</v>
       </c>
@@ -42612,7 +42612,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="358" spans="1:30">
+    <row r="358" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A358" s="3" t="s">
         <v>1170</v>
       </c>
@@ -42707,7 +42707,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="359" spans="1:30">
+    <row r="359" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A359" s="3" t="s">
         <v>1173</v>
       </c>
@@ -42802,7 +42802,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="360" spans="1:30">
+    <row r="360" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A360" s="3" t="s">
         <v>1176</v>
       </c>
@@ -42897,7 +42897,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="361" spans="1:30">
+    <row r="361" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A361" s="3" t="s">
         <v>1179</v>
       </c>
@@ -42992,7 +42992,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="362" spans="1:30">
+    <row r="362" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A362" s="3" t="s">
         <v>1182</v>
       </c>
@@ -43087,7 +43087,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="363" spans="1:30">
+    <row r="363" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A363" s="3" t="s">
         <v>1185</v>
       </c>
@@ -43182,7 +43182,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="364" spans="1:30">
+    <row r="364" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A364" s="3" t="s">
         <v>1188</v>
       </c>
@@ -43277,7 +43277,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="365" spans="1:30">
+    <row r="365" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A365" s="3" t="s">
         <v>1191</v>
       </c>
@@ -43372,7 +43372,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="366" spans="1:30">
+    <row r="366" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A366" s="3" t="s">
         <v>1194</v>
       </c>
@@ -43467,7 +43467,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="367" spans="1:30">
+    <row r="367" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A367" s="3" t="s">
         <v>1197</v>
       </c>
@@ -43562,7 +43562,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="368" spans="1:30">
+    <row r="368" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A368" s="3" t="s">
         <v>1200</v>
       </c>
@@ -43657,7 +43657,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="369" spans="1:30">
+    <row r="369" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A369" s="3" t="s">
         <v>1203</v>
       </c>
@@ -43752,7 +43752,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="370" spans="1:30">
+    <row r="370" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A370" s="3" t="s">
         <v>1206</v>
       </c>
@@ -43847,7 +43847,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="371" spans="1:30">
+    <row r="371" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A371" s="3" t="s">
         <v>1209</v>
       </c>
@@ -43942,7 +43942,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="372" spans="1:30">
+    <row r="372" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A372" s="3" t="s">
         <v>1212</v>
       </c>
@@ -44037,7 +44037,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="373" spans="1:30">
+    <row r="373" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A373" s="3" t="s">
         <v>1215</v>
       </c>
@@ -44132,7 +44132,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="374" spans="1:30">
+    <row r="374" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A374" s="3" t="s">
         <v>1218</v>
       </c>
@@ -44227,7 +44227,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="375" spans="1:30">
+    <row r="375" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A375" s="3" t="s">
         <v>1220</v>
       </c>
@@ -44322,7 +44322,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="376" spans="1:30">
+    <row r="376" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A376" s="3" t="s">
         <v>1223</v>
       </c>
@@ -44417,7 +44417,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="377" spans="1:30">
+    <row r="377" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A377" s="3" t="s">
         <v>1226</v>
       </c>
@@ -44512,7 +44512,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="378" spans="1:30">
+    <row r="378" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A378" s="3" t="s">
         <v>1229</v>
       </c>
@@ -44607,7 +44607,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="379" spans="1:30">
+    <row r="379" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A379" s="3" t="s">
         <v>1232</v>
       </c>
@@ -44702,7 +44702,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="380" spans="1:30">
+    <row r="380" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A380" s="3" t="s">
         <v>1235</v>
       </c>
@@ -44797,7 +44797,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="381" spans="1:30">
+    <row r="381" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A381" s="3" t="s">
         <v>1238</v>
       </c>
@@ -44892,7 +44892,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="382" spans="1:30">
+    <row r="382" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A382" s="3" t="s">
         <v>1241</v>
       </c>
@@ -44987,7 +44987,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="383" spans="1:30">
+    <row r="383" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A383" s="3" t="s">
         <v>1244</v>
       </c>
@@ -45082,7 +45082,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="384" spans="1:30">
+    <row r="384" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A384" s="3" t="s">
         <v>1247</v>
       </c>
@@ -45177,7 +45177,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="385" spans="1:30">
+    <row r="385" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A385" s="3" t="s">
         <v>1249</v>
       </c>
@@ -45272,7 +45272,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="386" spans="1:30">
+    <row r="386" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A386" s="3" t="s">
         <v>1252</v>
       </c>
@@ -45367,7 +45367,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="387" spans="1:30">
+    <row r="387" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A387" s="3" t="s">
         <v>1255</v>
       </c>
@@ -45463,7 +45463,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="388" spans="1:30">
+    <row r="388" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A388" s="3" t="s">
         <v>1258</v>
       </c>
@@ -45558,7 +45558,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="389" spans="1:30">
+    <row r="389" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A389" s="3" t="s">
         <v>1261</v>
       </c>
@@ -45653,7 +45653,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="390" spans="1:30">
+    <row r="390" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A390" s="3" t="s">
         <v>1264</v>
       </c>
@@ -45748,7 +45748,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="391" spans="1:30">
+    <row r="391" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A391" s="3" t="s">
         <v>1267</v>
       </c>
@@ -45843,7 +45843,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="392" spans="1:30">
+    <row r="392" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A392" s="3" t="s">
         <v>1270</v>
       </c>
@@ -45938,7 +45938,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="393" spans="1:30">
+    <row r="393" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A393" s="3" t="s">
         <v>1273</v>
       </c>
@@ -46033,7 +46033,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="394" spans="1:30">
+    <row r="394" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A394" s="3" t="s">
         <v>1276</v>
       </c>
@@ -46128,7 +46128,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="395" spans="1:30">
+    <row r="395" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A395" s="3" t="s">
         <v>1279</v>
       </c>
@@ -46223,7 +46223,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="396" spans="1:30">
+    <row r="396" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A396" s="3" t="s">
         <v>1282</v>
       </c>
@@ -46318,7 +46318,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="397" spans="1:30">
+    <row r="397" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A397" s="3" t="s">
         <v>1285</v>
       </c>
@@ -46413,7 +46413,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="398" spans="1:30">
+    <row r="398" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A398" s="3" t="s">
         <v>1288</v>
       </c>
@@ -46508,7 +46508,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="399" spans="1:30">
+    <row r="399" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A399" s="3" t="s">
         <v>1291</v>
       </c>
@@ -46603,7 +46603,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="400" spans="1:30">
+    <row r="400" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A400" s="3" t="s">
         <v>1294</v>
       </c>
@@ -46698,7 +46698,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="401" spans="1:30">
+    <row r="401" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A401" s="3" t="s">
         <v>1297</v>
       </c>
@@ -46793,7 +46793,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="402" spans="1:30">
+    <row r="402" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A402" s="3" t="s">
         <v>1300</v>
       </c>
@@ -46888,7 +46888,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="403" spans="1:30">
+    <row r="403" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A403" s="3" t="s">
         <v>1303</v>
       </c>
@@ -46983,7 +46983,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="404" spans="1:30">
+    <row r="404" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A404" s="3" t="s">
         <v>1306</v>
       </c>
@@ -47078,7 +47078,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="405" spans="1:30">
+    <row r="405" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A405" s="3" t="s">
         <v>1309</v>
       </c>
@@ -47173,7 +47173,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="406" spans="1:30">
+    <row r="406" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A406" s="3" t="s">
         <v>1312</v>
       </c>
@@ -47268,7 +47268,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="407" spans="1:30">
+    <row r="407" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A407" s="3" t="s">
         <v>1315</v>
       </c>
@@ -47363,7 +47363,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="408" spans="1:30">
+    <row r="408" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A408" s="3" t="s">
         <v>1318</v>
       </c>
@@ -47458,7 +47458,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="409" spans="1:30">
+    <row r="409" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A409" s="3" t="s">
         <v>1321</v>
       </c>
@@ -47553,7 +47553,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="410" spans="1:30">
+    <row r="410" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A410" s="3" t="s">
         <v>1324</v>
       </c>
@@ -47648,7 +47648,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="411" spans="1:30">
+    <row r="411" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A411" s="3" t="s">
         <v>1327</v>
       </c>
@@ -47743,7 +47743,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="412" spans="1:30">
+    <row r="412" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A412" s="3" t="s">
         <v>1330</v>
       </c>
@@ -47838,7 +47838,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="413" spans="1:30">
+    <row r="413" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A413" s="3" t="s">
         <v>1333</v>
       </c>
@@ -47933,7 +47933,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="414" spans="1:30">
+    <row r="414" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A414" s="3" t="s">
         <v>1336</v>
       </c>
@@ -48028,7 +48028,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="415" spans="1:30">
+    <row r="415" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A415" s="3" t="s">
         <v>1339</v>
       </c>
@@ -48123,7 +48123,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="416" spans="1:30">
+    <row r="416" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A416" s="3" t="s">
         <v>1342</v>
       </c>
@@ -48218,7 +48218,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="417" spans="1:30">
+    <row r="417" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A417" s="3" t="s">
         <v>1345</v>
       </c>
@@ -48313,7 +48313,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="418" spans="1:30">
+    <row r="418" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A418" s="3" t="s">
         <v>1348</v>
       </c>
@@ -48408,7 +48408,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="419" spans="1:30">
+    <row r="419" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A419" s="3" t="s">
         <v>1351</v>
       </c>
@@ -48503,7 +48503,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="420" spans="1:30">
+    <row r="420" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A420" s="3" t="s">
         <v>1354</v>
       </c>
@@ -48598,7 +48598,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="421" spans="1:30">
+    <row r="421" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A421" s="3" t="s">
         <v>1357</v>
       </c>
@@ -48693,7 +48693,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="422" spans="1:30">
+    <row r="422" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A422" s="3" t="s">
         <v>1360</v>
       </c>
@@ -48788,7 +48788,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="423" spans="1:30">
+    <row r="423" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A423" s="3" t="s">
         <v>1363</v>
       </c>
@@ -48883,7 +48883,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="424" spans="1:30">
+    <row r="424" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A424" s="3" t="s">
         <v>1366</v>
       </c>
@@ -48978,7 +48978,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="425" spans="1:30">
+    <row r="425" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A425" s="3" t="s">
         <v>1369</v>
       </c>
@@ -49073,7 +49073,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="426" spans="1:30">
+    <row r="426" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A426" s="3" t="s">
         <v>1372</v>
       </c>
@@ -49168,7 +49168,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="427" spans="1:30">
+    <row r="427" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A427" s="3" t="s">
         <v>1375</v>
       </c>
@@ -49263,7 +49263,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="428" spans="1:30">
+    <row r="428" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A428" s="3" t="s">
         <v>1378</v>
       </c>
@@ -49358,7 +49358,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="429" spans="1:30">
+    <row r="429" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A429" s="3" t="s">
         <v>1381</v>
       </c>
@@ -49453,7 +49453,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="430" spans="1:30">
+    <row r="430" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A430" s="3" t="s">
         <v>1384</v>
       </c>
@@ -49548,7 +49548,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="431" spans="1:30">
+    <row r="431" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A431" s="3" t="s">
         <v>1387</v>
       </c>
@@ -49643,7 +49643,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="432" spans="1:30">
+    <row r="432" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A432" s="3" t="s">
         <v>1390</v>
       </c>
@@ -49738,7 +49738,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="433" spans="1:30">
+    <row r="433" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A433" s="3" t="s">
         <v>1393</v>
       </c>
@@ -49833,7 +49833,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="434" spans="1:30">
+    <row r="434" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A434" s="3" t="s">
         <v>1396</v>
       </c>
@@ -49928,7 +49928,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="435" spans="1:30">
+    <row r="435" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A435" s="3" t="s">
         <v>1399</v>
       </c>
@@ -50023,7 +50023,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="436" spans="1:30">
+    <row r="436" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A436" s="3" t="s">
         <v>1402</v>
       </c>
@@ -50118,7 +50118,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="437" spans="1:30">
+    <row r="437" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A437" s="3" t="s">
         <v>1405</v>
       </c>
@@ -50213,7 +50213,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="438" spans="1:30">
+    <row r="438" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A438" s="3" t="s">
         <v>1408</v>
       </c>
@@ -50308,7 +50308,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="439" spans="1:30">
+    <row r="439" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A439" s="3" t="s">
         <v>1411</v>
       </c>
@@ -50403,7 +50403,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="440" spans="1:30">
+    <row r="440" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A440" s="3" t="s">
         <v>1414</v>
       </c>
@@ -50498,7 +50498,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="441" spans="1:30">
+    <row r="441" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A441" s="3" t="s">
         <v>1417</v>
       </c>
@@ -50593,7 +50593,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="442" spans="1:30">
+    <row r="442" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A442" s="3" t="s">
         <v>1420</v>
       </c>
@@ -50688,7 +50688,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="443" spans="1:30">
+    <row r="443" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A443" s="3" t="s">
         <v>1422</v>
       </c>
@@ -50783,7 +50783,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="444" spans="1:30">
+    <row r="444" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A444" s="3" t="s">
         <v>1425</v>
       </c>
@@ -50878,7 +50878,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="445" spans="1:30">
+    <row r="445" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A445" s="3" t="s">
         <v>1428</v>
       </c>
@@ -50973,7 +50973,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="446" spans="1:30">
+    <row r="446" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A446" s="3" t="s">
         <v>1431</v>
       </c>
@@ -51068,7 +51068,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="447" spans="1:30">
+    <row r="447" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A447" s="3" t="s">
         <v>1434</v>
       </c>
@@ -51163,7 +51163,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="448" spans="1:30">
+    <row r="448" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A448" s="3" t="s">
         <v>1437</v>
       </c>
@@ -51258,7 +51258,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="449" spans="1:30">
+    <row r="449" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A449" s="3" t="s">
         <v>1440</v>
       </c>
@@ -51353,7 +51353,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="450" spans="1:30">
+    <row r="450" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A450" s="3" t="s">
         <v>1443</v>
       </c>
@@ -51448,7 +51448,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="451" spans="1:30">
+    <row r="451" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A451" s="3" t="s">
         <v>1446</v>
       </c>
@@ -51544,7 +51544,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="452" spans="1:30">
+    <row r="452" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A452" s="3" t="s">
         <v>1448</v>
       </c>
@@ -51639,7 +51639,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="453" spans="1:30">
+    <row r="453" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A453" s="3" t="s">
         <v>1451</v>
       </c>
@@ -51734,7 +51734,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="454" spans="1:30">
+    <row r="454" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A454" s="3" t="s">
         <v>1454</v>
       </c>
@@ -51829,7 +51829,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="455" spans="1:30">
+    <row r="455" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A455" s="3" t="s">
         <v>1457</v>
       </c>
@@ -51924,7 +51924,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="456" spans="1:30">
+    <row r="456" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A456" s="3" t="s">
         <v>1460</v>
       </c>
@@ -52019,7 +52019,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="457" spans="1:30">
+    <row r="457" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A457" s="3" t="s">
         <v>1463</v>
       </c>
@@ -52114,7 +52114,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="458" spans="1:30">
+    <row r="458" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A458" s="3" t="s">
         <v>1466</v>
       </c>
@@ -52209,7 +52209,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="459" spans="1:30">
+    <row r="459" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A459" s="3" t="s">
         <v>1469</v>
       </c>
@@ -52304,7 +52304,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="460" spans="1:30">
+    <row r="460" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A460" s="3" t="s">
         <v>1472</v>
       </c>
@@ -52399,7 +52399,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="461" spans="1:30">
+    <row r="461" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A461" s="3" t="s">
         <v>1475</v>
       </c>
@@ -52494,7 +52494,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="462" spans="1:30">
+    <row r="462" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A462" s="3" t="s">
         <v>1478</v>
       </c>
@@ -52589,7 +52589,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="463" spans="1:30">
+    <row r="463" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A463" s="3" t="s">
         <v>1481</v>
       </c>
@@ -52684,7 +52684,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="464" spans="1:30">
+    <row r="464" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A464" s="3" t="s">
         <v>1484</v>
       </c>
@@ -52779,7 +52779,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="465" spans="1:30">
+    <row r="465" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A465" s="3" t="s">
         <v>1487</v>
       </c>
@@ -52874,7 +52874,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="466" spans="1:30">
+    <row r="466" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A466" s="3" t="s">
         <v>1490</v>
       </c>
@@ -52969,7 +52969,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="467" spans="1:30">
+    <row r="467" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A467" s="3" t="s">
         <v>1493</v>
       </c>
@@ -53064,7 +53064,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="468" spans="1:30">
+    <row r="468" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A468" s="3" t="s">
         <v>1496</v>
       </c>
@@ -53159,7 +53159,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="469" spans="1:30">
+    <row r="469" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A469" s="3" t="s">
         <v>1499</v>
       </c>
@@ -53254,7 +53254,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="470" spans="1:30">
+    <row r="470" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A470" s="3" t="s">
         <v>1502</v>
       </c>
@@ -53349,7 +53349,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="471" spans="1:30">
+    <row r="471" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A471" s="3" t="s">
         <v>1505</v>
       </c>
@@ -53444,7 +53444,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="472" spans="1:30">
+    <row r="472" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A472" s="3" t="s">
         <v>1508</v>
       </c>
@@ -53539,7 +53539,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="473" spans="1:30">
+    <row r="473" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A473" s="3" t="s">
         <v>1511</v>
       </c>
@@ -53634,7 +53634,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="474" spans="1:30">
+    <row r="474" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A474" s="3" t="s">
         <v>1514</v>
       </c>
@@ -53729,7 +53729,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="475" spans="1:30">
+    <row r="475" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A475" s="3" t="s">
         <v>1517</v>
       </c>
@@ -53824,7 +53824,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="476" spans="1:30">
+    <row r="476" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A476" s="3" t="s">
         <v>1520</v>
       </c>
@@ -53919,7 +53919,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="477" spans="1:30">
+    <row r="477" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A477" s="3" t="s">
         <v>1523</v>
       </c>
@@ -54014,7 +54014,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="478" spans="1:30">
+    <row r="478" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A478" s="3" t="s">
         <v>1526</v>
       </c>
@@ -54109,7 +54109,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="479" spans="1:30">
+    <row r="479" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A479" s="3" t="s">
         <v>1529</v>
       </c>
@@ -54204,7 +54204,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="480" spans="1:30">
+    <row r="480" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A480" s="3" t="s">
         <v>1532</v>
       </c>
@@ -54299,7 +54299,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="481" spans="1:30">
+    <row r="481" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A481" s="3" t="s">
         <v>1535</v>
       </c>
@@ -54394,7 +54394,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="482" spans="1:30">
+    <row r="482" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A482" s="3" t="s">
         <v>1538</v>
       </c>
@@ -54489,7 +54489,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="483" spans="1:30">
+    <row r="483" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A483" s="3" t="s">
         <v>1541</v>
       </c>
@@ -54584,7 +54584,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="484" spans="1:30">
+    <row r="484" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A484" s="3" t="s">
         <v>1544</v>
       </c>
@@ -54679,7 +54679,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="485" spans="1:30">
+    <row r="485" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A485" s="3" t="s">
         <v>1547</v>
       </c>
@@ -54774,7 +54774,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="486" spans="1:30">
+    <row r="486" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A486" s="3" t="s">
         <v>1550</v>
       </c>
@@ -54869,7 +54869,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="487" spans="1:30">
+    <row r="487" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A487" s="3" t="s">
         <v>1553</v>
       </c>
@@ -54964,7 +54964,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="488" spans="1:30">
+    <row r="488" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A488" s="3" t="s">
         <v>1556</v>
       </c>
@@ -55059,7 +55059,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="489" spans="1:30">
+    <row r="489" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A489" s="3" t="s">
         <v>1559</v>
       </c>
@@ -55154,7 +55154,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="490" spans="1:30">
+    <row r="490" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A490" s="3" t="s">
         <v>1562</v>
       </c>
@@ -55249,7 +55249,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="491" spans="1:30">
+    <row r="491" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A491" s="3" t="s">
         <v>1565</v>
       </c>
@@ -55344,7 +55344,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="492" spans="1:30">
+    <row r="492" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A492" s="3" t="s">
         <v>1568</v>
       </c>
@@ -55439,7 +55439,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="493" spans="1:30">
+    <row r="493" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A493" s="3" t="s">
         <v>1571</v>
       </c>
@@ -55534,7 +55534,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="494" spans="1:30">
+    <row r="494" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A494" s="3" t="s">
         <v>1574</v>
       </c>
@@ -55629,7 +55629,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="495" spans="1:30">
+    <row r="495" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A495" s="3" t="s">
         <v>1577</v>
       </c>
@@ -55724,7 +55724,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="496" spans="1:30">
+    <row r="496" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A496" s="3" t="s">
         <v>1580</v>
       </c>
@@ -55819,7 +55819,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="497" spans="1:30">
+    <row r="497" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A497" s="3" t="s">
         <v>1583</v>
       </c>
@@ -55914,7 +55914,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="498" spans="1:30">
+    <row r="498" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A498" s="3" t="s">
         <v>1586</v>
       </c>
@@ -56009,7 +56009,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="499" spans="1:30">
+    <row r="499" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A499" s="3" t="s">
         <v>1589</v>
       </c>
@@ -56104,7 +56104,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="500" spans="1:30">
+    <row r="500" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A500" s="3" t="s">
         <v>1592</v>
       </c>
@@ -56199,7 +56199,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="501" spans="1:30">
+    <row r="501" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A501" s="3" t="s">
         <v>1595</v>
       </c>
@@ -56294,7 +56294,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="502" spans="1:30">
+    <row r="502" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A502" s="3" t="s">
         <v>1598</v>
       </c>
@@ -56389,7 +56389,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="503" spans="1:30">
+    <row r="503" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A503" s="3" t="s">
         <v>1601</v>
       </c>
@@ -56484,7 +56484,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="504" spans="1:30">
+    <row r="504" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A504" s="3" t="s">
         <v>1603</v>
       </c>
@@ -56579,7 +56579,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="505" spans="1:30">
+    <row r="505" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A505" s="3" t="s">
         <v>1606</v>
       </c>
@@ -56674,7 +56674,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="506" spans="1:30">
+    <row r="506" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A506" s="3" t="s">
         <v>1609</v>
       </c>
@@ -56769,7 +56769,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="507" spans="1:30">
+    <row r="507" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A507" s="3" t="s">
         <v>1612</v>
       </c>
@@ -56864,7 +56864,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="508" spans="1:30">
+    <row r="508" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A508" s="3" t="s">
         <v>1615</v>
       </c>
@@ -56959,7 +56959,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="509" spans="1:30">
+    <row r="509" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A509" s="3" t="s">
         <v>1618</v>
       </c>
@@ -57054,7 +57054,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="510" spans="1:30">
+    <row r="510" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A510" s="3" t="s">
         <v>1621</v>
       </c>
@@ -57149,7 +57149,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="511" spans="1:30">
+    <row r="511" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A511" s="3" t="s">
         <v>1624</v>
       </c>
@@ -57244,7 +57244,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="512" spans="1:30">
+    <row r="512" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A512" s="3" t="s">
         <v>1627</v>
       </c>
@@ -57339,7 +57339,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="513" spans="1:30">
+    <row r="513" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A513" s="3" t="s">
         <v>1630</v>
       </c>
@@ -57434,7 +57434,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="514" spans="1:30">
+    <row r="514" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A514" s="3" t="s">
         <v>1633</v>
       </c>
@@ -57529,7 +57529,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="515" spans="1:30">
+    <row r="515" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A515" s="3" t="s">
         <v>1635</v>
       </c>
@@ -57625,7 +57625,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="516" spans="1:30">
+    <row r="516" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A516" s="3" t="s">
         <v>1638</v>
       </c>
@@ -57720,7 +57720,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="517" spans="1:30">
+    <row r="517" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A517" s="3" t="s">
         <v>1641</v>
       </c>
@@ -57815,7 +57815,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="518" spans="1:30">
+    <row r="518" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A518" s="3" t="s">
         <v>1644</v>
       </c>
@@ -57910,7 +57910,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="519" spans="1:30">
+    <row r="519" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A519" s="3" t="s">
         <v>1647</v>
       </c>
@@ -58005,7 +58005,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="520" spans="1:30">
+    <row r="520" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A520" s="3" t="s">
         <v>1650</v>
       </c>
@@ -58100,7 +58100,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="521" spans="1:30">
+    <row r="521" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A521" s="3" t="s">
         <v>1653</v>
       </c>
@@ -58195,7 +58195,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="522" spans="1:30">
+    <row r="522" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A522" s="3" t="s">
         <v>1656</v>
       </c>
@@ -58290,7 +58290,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="523" spans="1:30">
+    <row r="523" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A523" s="3" t="s">
         <v>1659</v>
       </c>
@@ -58385,7 +58385,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="524" spans="1:30">
+    <row r="524" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A524" s="3" t="s">
         <v>1662</v>
       </c>
@@ -58480,7 +58480,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="525" spans="1:30">
+    <row r="525" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A525" s="3" t="s">
         <v>1665</v>
       </c>
@@ -58575,7 +58575,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="526" spans="1:30">
+    <row r="526" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A526" s="3" t="s">
         <v>1668</v>
       </c>
@@ -58670,7 +58670,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="527" spans="1:30">
+    <row r="527" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A527" s="3" t="s">
         <v>1671</v>
       </c>
@@ -58765,7 +58765,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="528" spans="1:30">
+    <row r="528" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A528" s="3" t="s">
         <v>1674</v>
       </c>
@@ -58860,7 +58860,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="529" spans="1:30">
+    <row r="529" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A529" s="3" t="s">
         <v>1677</v>
       </c>
@@ -58955,7 +58955,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="530" spans="1:30">
+    <row r="530" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A530" s="3" t="s">
         <v>1680</v>
       </c>
@@ -59050,7 +59050,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="531" spans="1:30">
+    <row r="531" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A531" s="3" t="s">
         <v>1683</v>
       </c>
@@ -59145,7 +59145,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="532" spans="1:30">
+    <row r="532" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A532" s="3" t="s">
         <v>1685</v>
       </c>
@@ -59240,7 +59240,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="533" spans="1:30">
+    <row r="533" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A533" s="3" t="s">
         <v>1688</v>
       </c>
@@ -59335,7 +59335,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="534" spans="1:30">
+    <row r="534" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A534" s="3" t="s">
         <v>1691</v>
       </c>
@@ -59430,7 +59430,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="535" spans="1:30">
+    <row r="535" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A535" s="3" t="s">
         <v>1694</v>
       </c>
@@ -59525,7 +59525,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="536" spans="1:30">
+    <row r="536" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A536" s="3" t="s">
         <v>1697</v>
       </c>
@@ -59620,7 +59620,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="537" spans="1:30">
+    <row r="537" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A537" s="3" t="s">
         <v>1700</v>
       </c>
@@ -59715,7 +59715,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="538" spans="1:30">
+    <row r="538" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A538" s="3" t="s">
         <v>1703</v>
       </c>
@@ -59810,7 +59810,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="539" spans="1:30">
+    <row r="539" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A539" s="3" t="s">
         <v>1706</v>
       </c>
@@ -59905,7 +59905,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="540" spans="1:30">
+    <row r="540" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A540" s="3" t="s">
         <v>1709</v>
       </c>
@@ -60000,7 +60000,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="541" spans="1:30">
+    <row r="541" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A541" s="3" t="s">
         <v>1712</v>
       </c>
@@ -60095,7 +60095,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="542" spans="1:30">
+    <row r="542" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A542" s="3" t="s">
         <v>1715</v>
       </c>
@@ -60190,7 +60190,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="543" spans="1:30">
+    <row r="543" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A543" s="3" t="s">
         <v>1718</v>
       </c>
@@ -60285,7 +60285,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="544" spans="1:30">
+    <row r="544" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A544" s="3" t="s">
         <v>1721</v>
       </c>
@@ -60380,7 +60380,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="545" spans="1:30">
+    <row r="545" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A545" s="3" t="s">
         <v>1724</v>
       </c>
@@ -60475,7 +60475,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="546" spans="1:30">
+    <row r="546" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A546" s="3" t="s">
         <v>1727</v>
       </c>
@@ -60570,7 +60570,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="547" spans="1:30">
+    <row r="547" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A547" s="3" t="s">
         <v>1730</v>
       </c>
@@ -60665,7 +60665,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="548" spans="1:30">
+    <row r="548" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A548" s="3" t="s">
         <v>1733</v>
       </c>
@@ -60760,7 +60760,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="549" spans="1:30">
+    <row r="549" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A549" s="3" t="s">
         <v>1736</v>
       </c>
@@ -60855,7 +60855,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="550" spans="1:30">
+    <row r="550" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A550" s="3" t="s">
         <v>1739</v>
       </c>
@@ -60950,7 +60950,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="551" spans="1:30">
+    <row r="551" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A551" s="3" t="s">
         <v>1742</v>
       </c>
@@ -61045,7 +61045,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="552" spans="1:30">
+    <row r="552" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A552" s="3" t="s">
         <v>1745</v>
       </c>
@@ -61140,7 +61140,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="553" spans="1:30">
+    <row r="553" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A553" s="3" t="s">
         <v>1748</v>
       </c>
@@ -61235,7 +61235,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="554" spans="1:30">
+    <row r="554" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A554" s="3" t="s">
         <v>1751</v>
       </c>
@@ -61330,7 +61330,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="555" spans="1:30">
+    <row r="555" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A555" s="3" t="s">
         <v>1754</v>
       </c>
@@ -61425,7 +61425,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="556" spans="1:30">
+    <row r="556" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A556" s="3" t="s">
         <v>1757</v>
       </c>
@@ -61520,7 +61520,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="557" spans="1:30">
+    <row r="557" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A557" s="3" t="s">
         <v>1760</v>
       </c>
@@ -61615,7 +61615,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="558" spans="1:30">
+    <row r="558" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A558" s="3" t="s">
         <v>1763</v>
       </c>
@@ -61710,7 +61710,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="559" spans="1:30">
+    <row r="559" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A559" s="3" t="s">
         <v>1766</v>
       </c>
@@ -61805,7 +61805,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="560" spans="1:30">
+    <row r="560" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A560" s="3" t="s">
         <v>1769</v>
       </c>
@@ -61900,7 +61900,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="561" spans="1:30">
+    <row r="561" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A561" s="3" t="s">
         <v>1772</v>
       </c>
@@ -61995,7 +61995,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="562" spans="1:30">
+    <row r="562" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A562" s="3" t="s">
         <v>1775</v>
       </c>
@@ -62090,7 +62090,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="563" spans="1:30">
+    <row r="563" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A563" s="3" t="s">
         <v>1778</v>
       </c>
@@ -62185,7 +62185,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="564" spans="1:30">
+    <row r="564" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A564" s="3" t="s">
         <v>1781</v>
       </c>
@@ -62280,7 +62280,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="565" spans="1:30">
+    <row r="565" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A565" s="3" t="s">
         <v>1784</v>
       </c>
@@ -62375,7 +62375,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="566" spans="1:30">
+    <row r="566" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A566" s="3" t="s">
         <v>1787</v>
       </c>
@@ -62470,7 +62470,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="567" spans="1:30">
+    <row r="567" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A567" s="3" t="s">
         <v>1790</v>
       </c>
@@ -62565,7 +62565,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="568" spans="1:30">
+    <row r="568" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A568" s="3" t="s">
         <v>1793</v>
       </c>
@@ -62660,7 +62660,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="569" spans="1:30">
+    <row r="569" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A569" s="3" t="s">
         <v>1796</v>
       </c>
@@ -62755,7 +62755,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="570" spans="1:30">
+    <row r="570" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A570" s="3" t="s">
         <v>1798</v>
       </c>
@@ -62850,7 +62850,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="571" spans="1:30">
+    <row r="571" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A571" s="3" t="s">
         <v>1801</v>
       </c>
@@ -62945,7 +62945,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="572" spans="1:30">
+    <row r="572" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A572" s="3" t="s">
         <v>1804</v>
       </c>
@@ -63040,7 +63040,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="573" spans="1:30">
+    <row r="573" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A573" s="3" t="s">
         <v>1807</v>
       </c>
@@ -63135,7 +63135,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="574" spans="1:30">
+    <row r="574" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A574" s="3" t="s">
         <v>1810</v>
       </c>
@@ -63230,7 +63230,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="575" spans="1:30">
+    <row r="575" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A575" s="3" t="s">
         <v>1813</v>
       </c>
@@ -63325,7 +63325,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="576" spans="1:30">
+    <row r="576" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A576" s="3" t="s">
         <v>1816</v>
       </c>
@@ -63420,7 +63420,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="577" spans="1:30">
+    <row r="577" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A577" s="3" t="s">
         <v>1818</v>
       </c>
@@ -63515,7 +63515,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="578" spans="1:30">
+    <row r="578" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A578" s="3" t="s">
         <v>1821</v>
       </c>
@@ -63610,7 +63610,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="579" spans="1:30">
+    <row r="579" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A579" s="3" t="s">
         <v>1824</v>
       </c>
@@ -63706,7 +63706,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="580" spans="1:30">
+    <row r="580" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A580" s="3" t="s">
         <v>1827</v>
       </c>
@@ -63801,7 +63801,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="581" spans="1:30">
+    <row r="581" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A581" s="3" t="s">
         <v>1829</v>
       </c>
@@ -63896,7 +63896,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="582" spans="1:30">
+    <row r="582" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A582" s="3" t="s">
         <v>1832</v>
       </c>
@@ -63991,7 +63991,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="583" spans="1:30">
+    <row r="583" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A583" s="3" t="s">
         <v>1835</v>
       </c>
@@ -64086,7 +64086,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="584" spans="1:30">
+    <row r="584" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A584" s="3" t="s">
         <v>1838</v>
       </c>
@@ -64181,7 +64181,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="585" spans="1:30">
+    <row r="585" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A585" s="3" t="s">
         <v>1841</v>
       </c>
@@ -64276,7 +64276,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="586" spans="1:30">
+    <row r="586" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A586" s="3" t="s">
         <v>1844</v>
       </c>
@@ -64371,7 +64371,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="587" spans="1:30">
+    <row r="587" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A587" s="3" t="s">
         <v>1847</v>
       </c>
@@ -64466,7 +64466,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="588" spans="1:30">
+    <row r="588" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A588" s="3" t="s">
         <v>1850</v>
       </c>
@@ -64561,7 +64561,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="589" spans="1:30">
+    <row r="589" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A589" s="3" t="s">
         <v>1853</v>
       </c>
@@ -64656,7 +64656,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="590" spans="1:30">
+    <row r="590" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A590" s="3" t="s">
         <v>1856</v>
       </c>
@@ -64751,7 +64751,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="591" spans="1:30">
+    <row r="591" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A591" s="3" t="s">
         <v>1859</v>
       </c>
@@ -64846,7 +64846,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="592" spans="1:30">
+    <row r="592" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A592" s="3" t="s">
         <v>1862</v>
       </c>
@@ -64941,7 +64941,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="593" spans="1:30">
+    <row r="593" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A593" s="3" t="s">
         <v>1865</v>
       </c>
@@ -65036,7 +65036,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="594" spans="1:30">
+    <row r="594" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A594" s="3" t="s">
         <v>1868</v>
       </c>
@@ -65131,7 +65131,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="595" spans="1:30">
+    <row r="595" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A595" s="3" t="s">
         <v>1871</v>
       </c>
@@ -65226,7 +65226,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="596" spans="1:30">
+    <row r="596" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A596" s="3" t="s">
         <v>1873</v>
       </c>
@@ -65321,7 +65321,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="597" spans="1:30">
+    <row r="597" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A597" s="3" t="s">
         <v>1876</v>
       </c>
@@ -65416,7 +65416,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="598" spans="1:30">
+    <row r="598" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A598" s="3" t="s">
         <v>1879</v>
       </c>
@@ -65511,7 +65511,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="599" spans="1:30">
+    <row r="599" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A599" s="3" t="s">
         <v>1882</v>
       </c>
@@ -65606,7 +65606,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="600" spans="1:30">
+    <row r="600" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A600" s="3" t="s">
         <v>1885</v>
       </c>
@@ -65701,7 +65701,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="601" spans="1:30">
+    <row r="601" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A601" s="3" t="s">
         <v>1888</v>
       </c>
@@ -65796,7 +65796,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="602" spans="1:30">
+    <row r="602" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A602" s="3" t="s">
         <v>1891</v>
       </c>
@@ -65891,7 +65891,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="603" spans="1:30">
+    <row r="603" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A603" s="3" t="s">
         <v>1894</v>
       </c>
@@ -65986,7 +65986,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="604" spans="1:30">
+    <row r="604" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A604" s="3" t="s">
         <v>1897</v>
       </c>
@@ -66081,7 +66081,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="605" spans="1:30">
+    <row r="605" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A605" s="3" t="s">
         <v>1900</v>
       </c>
@@ -66176,7 +66176,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="606" spans="1:30">
+    <row r="606" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A606" s="3" t="s">
         <v>1902</v>
       </c>
@@ -66271,7 +66271,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="607" spans="1:30">
+    <row r="607" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A607" s="3" t="s">
         <v>1905</v>
       </c>
@@ -66366,7 +66366,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="608" spans="1:30">
+    <row r="608" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A608" s="3" t="s">
         <v>1908</v>
       </c>
@@ -66461,7 +66461,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="609" spans="1:30">
+    <row r="609" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A609" s="3" t="s">
         <v>1911</v>
       </c>
@@ -66556,7 +66556,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="610" spans="1:30">
+    <row r="610" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A610" s="3" t="s">
         <v>1914</v>
       </c>
@@ -66651,7 +66651,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="611" spans="1:30">
+    <row r="611" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A611" s="3" t="s">
         <v>1916</v>
       </c>
@@ -66746,7 +66746,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="612" spans="1:30">
+    <row r="612" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A612" s="3" t="s">
         <v>1919</v>
       </c>
@@ -66841,7 +66841,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="613" spans="1:30">
+    <row r="613" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A613" s="3" t="s">
         <v>1921</v>
       </c>
@@ -66936,7 +66936,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="614" spans="1:30">
+    <row r="614" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A614" s="3" t="s">
         <v>1924</v>
       </c>
@@ -67031,7 +67031,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="615" spans="1:30">
+    <row r="615" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A615" s="3" t="s">
         <v>1927</v>
       </c>
@@ -67126,7 +67126,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="616" spans="1:30">
+    <row r="616" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A616" s="3" t="s">
         <v>1930</v>
       </c>
@@ -67221,7 +67221,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="617" spans="1:30">
+    <row r="617" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A617" s="3" t="s">
         <v>1933</v>
       </c>
@@ -67316,7 +67316,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="618" spans="1:30">
+    <row r="618" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A618" s="3" t="s">
         <v>1936</v>
       </c>
@@ -67411,7 +67411,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="619" spans="1:30">
+    <row r="619" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A619" s="3" t="s">
         <v>1939</v>
       </c>
@@ -67506,7 +67506,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="620" spans="1:30">
+    <row r="620" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A620" s="3" t="s">
         <v>1942</v>
       </c>
@@ -67601,7 +67601,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="621" spans="1:30">
+    <row r="621" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A621" s="3" t="s">
         <v>1945</v>
       </c>
@@ -67696,7 +67696,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="622" spans="1:30">
+    <row r="622" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A622" s="3" t="s">
         <v>1948</v>
       </c>
@@ -67791,7 +67791,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="623" spans="1:30">
+    <row r="623" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A623" s="3" t="s">
         <v>1951</v>
       </c>
@@ -67886,7 +67886,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="624" spans="1:30">
+    <row r="624" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A624" s="3" t="s">
         <v>1954</v>
       </c>
@@ -67981,7 +67981,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="625" spans="1:30">
+    <row r="625" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A625" s="3" t="s">
         <v>1957</v>
       </c>
@@ -68076,7 +68076,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="626" spans="1:30">
+    <row r="626" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A626" s="3" t="s">
         <v>1960</v>
       </c>
@@ -68171,7 +68171,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="627" spans="1:30">
+    <row r="627" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A627" s="3" t="s">
         <v>1963</v>
       </c>
@@ -68266,7 +68266,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="628" spans="1:30">
+    <row r="628" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A628" s="3" t="s">
         <v>1966</v>
       </c>
@@ -68361,7 +68361,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="629" spans="1:30">
+    <row r="629" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A629" s="3" t="s">
         <v>1969</v>
       </c>
@@ -68456,7 +68456,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="630" spans="1:30">
+    <row r="630" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A630" s="3" t="s">
         <v>1972</v>
       </c>
@@ -68551,7 +68551,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="631" spans="1:30">
+    <row r="631" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A631" s="3" t="s">
         <v>1975</v>
       </c>
@@ -68646,7 +68646,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="632" spans="1:30">
+    <row r="632" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A632" s="3" t="s">
         <v>1978</v>
       </c>
@@ -68741,7 +68741,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="633" spans="1:30">
+    <row r="633" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A633" s="3" t="s">
         <v>1981</v>
       </c>
@@ -68836,7 +68836,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="634" spans="1:30">
+    <row r="634" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A634" s="3" t="s">
         <v>1984</v>
       </c>
@@ -68931,7 +68931,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="635" spans="1:30">
+    <row r="635" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A635" s="3" t="s">
         <v>1987</v>
       </c>
@@ -69026,7 +69026,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="636" spans="1:30">
+    <row r="636" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A636" s="3" t="s">
         <v>1990</v>
       </c>
@@ -69121,7 +69121,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="637" spans="1:30">
+    <row r="637" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A637" s="3" t="s">
         <v>1993</v>
       </c>
@@ -69216,7 +69216,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="638" spans="1:30">
+    <row r="638" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A638" s="3" t="s">
         <v>1996</v>
       </c>
@@ -69311,7 +69311,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="639" spans="1:30">
+    <row r="639" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A639" s="3" t="s">
         <v>1999</v>
       </c>
@@ -69406,7 +69406,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="640" spans="1:30">
+    <row r="640" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A640" s="3" t="s">
         <v>2002</v>
       </c>
@@ -69501,7 +69501,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="641" spans="1:30">
+    <row r="641" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A641" s="3" t="s">
         <v>2005</v>
       </c>
@@ -69596,7 +69596,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="642" spans="1:30">
+    <row r="642" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A642" s="3" t="s">
         <v>2008</v>
       </c>
@@ -69691,7 +69691,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="643" spans="1:30">
+    <row r="643" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A643" s="3" t="s">
         <v>2011</v>
       </c>
@@ -69787,7 +69787,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="644" spans="1:30">
+    <row r="644" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A644" s="3" t="s">
         <v>2014</v>
       </c>
@@ -69882,7 +69882,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="645" spans="1:30">
+    <row r="645" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A645" s="3" t="s">
         <v>2017</v>
       </c>
@@ -69977,7 +69977,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="646" spans="1:30">
+    <row r="646" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A646" s="3" t="s">
         <v>2019</v>
       </c>
@@ -70072,7 +70072,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="647" spans="1:30">
+    <row r="647" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A647" s="3" t="s">
         <v>2022</v>
       </c>
@@ -70167,7 +70167,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="648" spans="1:30">
+    <row r="648" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A648" s="3" t="s">
         <v>2025</v>
       </c>
@@ -70262,7 +70262,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="649" spans="1:30">
+    <row r="649" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A649" s="3" t="s">
         <v>2028</v>
       </c>
@@ -70357,7 +70357,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="650" spans="1:30">
+    <row r="650" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A650" s="3" t="s">
         <v>2031</v>
       </c>
@@ -70452,7 +70452,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="651" spans="1:30">
+    <row r="651" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A651" s="3" t="s">
         <v>2034</v>
       </c>
@@ -70547,7 +70547,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="652" spans="1:30">
+    <row r="652" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A652" s="3" t="s">
         <v>2037</v>
       </c>
@@ -70642,7 +70642,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="653" spans="1:30">
+    <row r="653" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A653" s="3" t="s">
         <v>2039</v>
       </c>
@@ -70737,7 +70737,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="654" spans="1:30">
+    <row r="654" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A654" s="3" t="s">
         <v>2042</v>
       </c>
@@ -70832,7 +70832,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="655" spans="1:30">
+    <row r="655" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A655" s="3" t="s">
         <v>2044</v>
       </c>
@@ -70927,7 +70927,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="656" spans="1:30">
+    <row r="656" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A656" s="3" t="s">
         <v>2047</v>
       </c>
@@ -71022,7 +71022,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="657" spans="1:30">
+    <row r="657" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A657" s="3" t="s">
         <v>2049</v>
       </c>
@@ -71117,7 +71117,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="658" spans="1:30">
+    <row r="658" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A658" s="3" t="s">
         <v>2052</v>
       </c>
@@ -71212,7 +71212,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="659" spans="1:30">
+    <row r="659" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A659" s="3" t="s">
         <v>2055</v>
       </c>
@@ -71307,7 +71307,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="660" spans="1:30">
+    <row r="660" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A660" s="3" t="s">
         <v>2058</v>
       </c>
@@ -71402,7 +71402,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="661" spans="1:30">
+    <row r="661" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A661" s="3" t="s">
         <v>2061</v>
       </c>
@@ -71497,7 +71497,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="662" spans="1:30">
+    <row r="662" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A662" s="3" t="s">
         <v>2064</v>
       </c>
@@ -71592,7 +71592,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="663" spans="1:30">
+    <row r="663" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A663" s="3" t="s">
         <v>2067</v>
       </c>
@@ -71687,7 +71687,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="664" spans="1:30">
+    <row r="664" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A664" s="3" t="s">
         <v>2070</v>
       </c>
@@ -71782,7 +71782,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="665" spans="1:30">
+    <row r="665" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A665" s="3" t="s">
         <v>2073</v>
       </c>
@@ -71877,7 +71877,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="666" spans="1:30">
+    <row r="666" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A666" s="3" t="s">
         <v>2076</v>
       </c>
@@ -71972,7 +71972,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="667" spans="1:30">
+    <row r="667" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A667" s="3" t="s">
         <v>2079</v>
       </c>
@@ -72067,7 +72067,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="668" spans="1:30">
+    <row r="668" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A668" s="3" t="s">
         <v>2082</v>
       </c>
@@ -72162,7 +72162,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="669" spans="1:30">
+    <row r="669" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A669" s="3" t="s">
         <v>2085</v>
       </c>
@@ -72257,7 +72257,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="670" spans="1:30">
+    <row r="670" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A670" s="3" t="s">
         <v>2088</v>
       </c>
@@ -72352,7 +72352,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="671" spans="1:30">
+    <row r="671" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A671" s="3" t="s">
         <v>2091</v>
       </c>
@@ -72447,7 +72447,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="672" spans="1:30">
+    <row r="672" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A672" s="3" t="s">
         <v>2094</v>
       </c>
@@ -72542,7 +72542,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="673" spans="1:30">
+    <row r="673" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A673" s="3" t="s">
         <v>2096</v>
       </c>
@@ -72637,7 +72637,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="674" spans="1:30">
+    <row r="674" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A674" s="3" t="s">
         <v>2099</v>
       </c>
@@ -72732,7 +72732,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="675" spans="1:30">
+    <row r="675" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A675" s="3" t="s">
         <v>2102</v>
       </c>
@@ -72827,7 +72827,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="676" spans="1:30">
+    <row r="676" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A676" s="3" t="s">
         <v>2105</v>
       </c>
@@ -72922,7 +72922,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="677" spans="1:30">
+    <row r="677" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A677" s="3" t="s">
         <v>2108</v>
       </c>
@@ -73017,7 +73017,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="678" spans="1:30">
+    <row r="678" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A678" s="3" t="s">
         <v>2110</v>
       </c>
@@ -73112,7 +73112,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="679" spans="1:30">
+    <row r="679" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A679" s="3" t="s">
         <v>2113</v>
       </c>
@@ -73207,7 +73207,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="680" spans="1:30">
+    <row r="680" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A680" s="3" t="s">
         <v>2115</v>
       </c>
@@ -73302,7 +73302,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="681" spans="1:30">
+    <row r="681" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A681" s="3" t="s">
         <v>2118</v>
       </c>
@@ -73397,7 +73397,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="682" spans="1:30">
+    <row r="682" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A682" s="3" t="s">
         <v>2121</v>
       </c>
@@ -73492,7 +73492,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="683" spans="1:30">
+    <row r="683" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A683" s="3" t="s">
         <v>2124</v>
       </c>
@@ -73587,7 +73587,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="684" spans="1:30">
+    <row r="684" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A684" s="3" t="s">
         <v>2127</v>
       </c>
@@ -73682,7 +73682,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="685" spans="1:30">
+    <row r="685" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A685" s="3" t="s">
         <v>2130</v>
       </c>
@@ -73777,7 +73777,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="686" spans="1:30">
+    <row r="686" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A686" s="3" t="s">
         <v>2133</v>
       </c>
@@ -73872,7 +73872,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="687" spans="1:30">
+    <row r="687" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A687" s="3" t="s">
         <v>2136</v>
       </c>
@@ -73967,7 +73967,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="688" spans="1:30">
+    <row r="688" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A688" s="3" t="s">
         <v>2138</v>
       </c>
@@ -74062,7 +74062,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="689" spans="1:30">
+    <row r="689" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A689" s="3" t="s">
         <v>2141</v>
       </c>
@@ -74157,7 +74157,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="690" spans="1:30">
+    <row r="690" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A690" s="3" t="s">
         <v>2144</v>
       </c>
@@ -74252,7 +74252,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="691" spans="1:30">
+    <row r="691" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A691" s="3" t="s">
         <v>2147</v>
       </c>
@@ -74347,7 +74347,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="692" spans="1:30">
+    <row r="692" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A692" s="3" t="s">
         <v>2150</v>
       </c>
@@ -74442,7 +74442,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="693" spans="1:30">
+    <row r="693" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A693" s="3" t="s">
         <v>2153</v>
       </c>
@@ -74537,7 +74537,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="694" spans="1:30">
+    <row r="694" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A694" s="3" t="s">
         <v>2156</v>
       </c>
@@ -74632,7 +74632,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="695" spans="1:30">
+    <row r="695" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A695" s="3" t="s">
         <v>2159</v>
       </c>
@@ -74727,7 +74727,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="696" spans="1:30">
+    <row r="696" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A696" s="3" t="s">
         <v>2162</v>
       </c>
@@ -74822,7 +74822,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="697" spans="1:30">
+    <row r="697" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A697" s="3" t="s">
         <v>2164</v>
       </c>
@@ -74917,7 +74917,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="698" spans="1:30">
+    <row r="698" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A698" s="3" t="s">
         <v>2167</v>
       </c>
@@ -75012,7 +75012,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="699" spans="1:30">
+    <row r="699" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A699" s="3" t="s">
         <v>2170</v>
       </c>
@@ -75107,7 +75107,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="700" spans="1:30">
+    <row r="700" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A700" s="3" t="s">
         <v>2173</v>
       </c>
@@ -75202,7 +75202,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="701" spans="1:30">
+    <row r="701" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A701" s="3" t="s">
         <v>2176</v>
       </c>
@@ -75297,7 +75297,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="702" spans="1:30">
+    <row r="702" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A702" s="3" t="s">
         <v>2179</v>
       </c>
@@ -75392,7 +75392,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="703" spans="1:30">
+    <row r="703" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A703" s="3" t="s">
         <v>2182</v>
       </c>
@@ -75487,7 +75487,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="704" spans="1:30">
+    <row r="704" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A704" s="3" t="s">
         <v>2185</v>
       </c>
@@ -75582,7 +75582,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="705" spans="1:30">
+    <row r="705" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A705" s="3" t="s">
         <v>2188</v>
       </c>
@@ -75677,7 +75677,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="706" spans="1:30">
+    <row r="706" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A706" s="3" t="s">
         <v>2191</v>
       </c>
@@ -75772,7 +75772,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="707" spans="1:30">
+    <row r="707" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A707" s="3" t="s">
         <v>2194</v>
       </c>
@@ -75868,7 +75868,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="708" spans="1:30">
+    <row r="708" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A708" s="3" t="s">
         <v>2197</v>
       </c>
@@ -75963,7 +75963,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="709" spans="1:30">
+    <row r="709" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A709" s="3" t="s">
         <v>2200</v>
       </c>
@@ -76058,7 +76058,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="710" spans="1:30">
+    <row r="710" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A710" s="3" t="s">
         <v>2203</v>
       </c>
@@ -76153,7 +76153,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="711" spans="1:30">
+    <row r="711" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A711" s="3" t="s">
         <v>2206</v>
       </c>
@@ -76248,7 +76248,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="712" spans="1:30">
+    <row r="712" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A712" s="3" t="s">
         <v>2209</v>
       </c>
@@ -76343,7 +76343,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="713" spans="1:30">
+    <row r="713" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A713" s="3" t="s">
         <v>2212</v>
       </c>
@@ -76438,7 +76438,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="714" spans="1:30">
+    <row r="714" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A714" s="3" t="s">
         <v>2215</v>
       </c>
@@ -76533,7 +76533,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="715" spans="1:30">
+    <row r="715" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A715" s="3" t="s">
         <v>2218</v>
       </c>
@@ -76628,7 +76628,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="716" spans="1:30">
+    <row r="716" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A716" s="3" t="s">
         <v>2220</v>
       </c>
@@ -76723,7 +76723,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="717" spans="1:30">
+    <row r="717" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A717" s="3" t="s">
         <v>2223</v>
       </c>
@@ -76818,7 +76818,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="718" spans="1:30">
+    <row r="718" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A718" s="3" t="s">
         <v>2226</v>
       </c>
@@ -76913,7 +76913,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="719" spans="1:30">
+    <row r="719" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A719" s="3" t="s">
         <v>2229</v>
       </c>
@@ -77008,7 +77008,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="720" spans="1:30">
+    <row r="720" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A720" s="3" t="s">
         <v>2232</v>
       </c>
@@ -77103,7 +77103,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="721" spans="1:30">
+    <row r="721" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A721" s="3" t="s">
         <v>2235</v>
       </c>
@@ -77198,7 +77198,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="722" spans="1:30">
+    <row r="722" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A722" s="3" t="s">
         <v>2237</v>
       </c>
@@ -77293,7 +77293,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="723" spans="1:30">
+    <row r="723" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A723" s="3" t="s">
         <v>2240</v>
       </c>
@@ -77388,7 +77388,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="724" spans="1:30">
+    <row r="724" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A724" s="3" t="s">
         <v>2243</v>
       </c>
@@ -77483,7 +77483,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="725" spans="1:30">
+    <row r="725" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A725" s="3" t="s">
         <v>2246</v>
       </c>
@@ -77578,7 +77578,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="726" spans="1:30">
+    <row r="726" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A726" s="3" t="s">
         <v>2249</v>
       </c>
@@ -77673,7 +77673,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="727" spans="1:30">
+    <row r="727" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A727" s="3" t="s">
         <v>2252</v>
       </c>
@@ -77768,7 +77768,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="728" spans="1:30">
+    <row r="728" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A728" s="3" t="s">
         <v>2255</v>
       </c>
@@ -77863,7 +77863,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="729" spans="1:30">
+    <row r="729" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A729" s="3" t="s">
         <v>2258</v>
       </c>
@@ -77958,7 +77958,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="730" spans="1:30">
+    <row r="730" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A730" s="3" t="s">
         <v>2261</v>
       </c>
@@ -78053,7 +78053,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="731" spans="1:30">
+    <row r="731" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A731" s="3" t="s">
         <v>2264</v>
       </c>
@@ -78148,7 +78148,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="732" spans="1:30">
+    <row r="732" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A732" s="3" t="s">
         <v>2267</v>
       </c>
@@ -78243,7 +78243,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="733" spans="1:30">
+    <row r="733" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A733" s="3" t="s">
         <v>2270</v>
       </c>
@@ -78338,7 +78338,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="734" spans="1:30">
+    <row r="734" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A734" s="3" t="s">
         <v>2273</v>
       </c>
@@ -78433,7 +78433,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="735" spans="1:30">
+    <row r="735" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A735" s="3" t="s">
         <v>2276</v>
       </c>
@@ -78528,7 +78528,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="736" spans="1:30">
+    <row r="736" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A736" s="3" t="s">
         <v>2279</v>
       </c>
@@ -78623,7 +78623,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="737" spans="1:30">
+    <row r="737" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A737" s="3" t="s">
         <v>2282</v>
       </c>
@@ -78718,7 +78718,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="738" spans="1:30">
+    <row r="738" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A738" s="3" t="s">
         <v>2285</v>
       </c>
@@ -78813,7 +78813,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="739" spans="1:30">
+    <row r="739" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A739" s="3" t="s">
         <v>2288</v>
       </c>
@@ -78908,7 +78908,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="740" spans="1:30">
+    <row r="740" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A740" s="3" t="s">
         <v>2291</v>
       </c>
@@ -79003,7 +79003,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="741" spans="1:30">
+    <row r="741" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A741" s="3" t="s">
         <v>2294</v>
       </c>
@@ -79098,7 +79098,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="742" spans="1:30">
+    <row r="742" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A742" s="3" t="s">
         <v>2297</v>
       </c>
@@ -79193,7 +79193,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="743" spans="1:30">
+    <row r="743" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A743" s="3" t="s">
         <v>2299</v>
       </c>
@@ -79288,7 +79288,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="744" spans="1:30">
+    <row r="744" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A744" s="3" t="s">
         <v>2302</v>
       </c>
@@ -79383,7 +79383,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="745" spans="1:30">
+    <row r="745" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A745" s="3" t="s">
         <v>2305</v>
       </c>
@@ -79478,7 +79478,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="746" spans="1:30">
+    <row r="746" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A746" s="3" t="s">
         <v>2308</v>
       </c>
@@ -79573,7 +79573,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="747" spans="1:30">
+    <row r="747" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A747" s="3" t="s">
         <v>2311</v>
       </c>
@@ -79668,7 +79668,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="748" spans="1:30">
+    <row r="748" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A748" s="3" t="s">
         <v>2314</v>
       </c>
@@ -79763,7 +79763,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="749" spans="1:30">
+    <row r="749" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A749" s="3" t="s">
         <v>2316</v>
       </c>
@@ -79858,7 +79858,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="750" spans="1:30">
+    <row r="750" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A750" s="3" t="s">
         <v>2319</v>
       </c>
@@ -79953,7 +79953,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="751" spans="1:30">
+    <row r="751" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A751" s="3" t="s">
         <v>2322</v>
       </c>
@@ -80048,7 +80048,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="752" spans="1:30">
+    <row r="752" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A752" s="3" t="s">
         <v>2325</v>
       </c>
@@ -80143,7 +80143,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="753" spans="1:30">
+    <row r="753" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A753" s="3" t="s">
         <v>2328</v>
       </c>
@@ -80238,7 +80238,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="754" spans="1:30">
+    <row r="754" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A754" s="3" t="s">
         <v>2331</v>
       </c>
@@ -80333,7 +80333,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="755" spans="1:30">
+    <row r="755" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A755" s="3" t="s">
         <v>2334</v>
       </c>
@@ -80428,7 +80428,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="756" spans="1:30">
+    <row r="756" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A756" s="3" t="s">
         <v>2337</v>
       </c>
@@ -80523,7 +80523,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="757" spans="1:30">
+    <row r="757" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A757" s="3" t="s">
         <v>2340</v>
       </c>
@@ -80618,7 +80618,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="758" spans="1:30">
+    <row r="758" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A758" s="3" t="s">
         <v>2343</v>
       </c>
@@ -80713,7 +80713,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="759" spans="1:30">
+    <row r="759" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A759" s="3" t="s">
         <v>2346</v>
       </c>
@@ -80808,7 +80808,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="760" spans="1:30">
+    <row r="760" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A760" s="3" t="s">
         <v>2349</v>
       </c>
@@ -80903,7 +80903,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="761" spans="1:30">
+    <row r="761" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A761" s="3" t="s">
         <v>2352</v>
       </c>
@@ -80998,7 +80998,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="762" spans="1:30">
+    <row r="762" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A762" s="3" t="s">
         <v>2355</v>
       </c>
@@ -81093,7 +81093,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="763" spans="1:30">
+    <row r="763" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A763" s="3" t="s">
         <v>2358</v>
       </c>
@@ -81188,7 +81188,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="764" spans="1:30">
+    <row r="764" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A764" s="3" t="s">
         <v>2361</v>
       </c>
@@ -81283,7 +81283,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="765" spans="1:30">
+    <row r="765" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A765" s="3" t="s">
         <v>2364</v>
       </c>
@@ -81378,7 +81378,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="766" spans="1:30">
+    <row r="766" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A766" s="3" t="s">
         <v>2367</v>
       </c>
@@ -81473,7 +81473,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="767" spans="1:30">
+    <row r="767" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A767" s="3" t="s">
         <v>2369</v>
       </c>
@@ -81568,7 +81568,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="768" spans="1:30">
+    <row r="768" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A768" s="3" t="s">
         <v>2372</v>
       </c>
@@ -81663,7 +81663,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="769" spans="1:30">
+    <row r="769" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A769" s="3" t="s">
         <v>2375</v>
       </c>
@@ -81758,7 +81758,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="770" spans="1:30">
+    <row r="770" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A770" s="3" t="s">
         <v>2378</v>
       </c>
@@ -81853,7 +81853,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="771" spans="1:30">
+    <row r="771" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A771" s="3" t="s">
         <v>2381</v>
       </c>
@@ -81949,7 +81949,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="772" spans="1:30">
+    <row r="772" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A772" s="3" t="s">
         <v>2384</v>
       </c>
@@ -82044,7 +82044,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="773" spans="1:30">
+    <row r="773" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A773" s="3" t="s">
         <v>2387</v>
       </c>
@@ -82139,7 +82139,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="774" spans="1:30">
+    <row r="774" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A774" s="3" t="s">
         <v>2389</v>
       </c>
@@ -82234,7 +82234,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="775" spans="1:30">
+    <row r="775" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A775" s="3" t="s">
         <v>2392</v>
       </c>
@@ -82329,7 +82329,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="776" spans="1:30">
+    <row r="776" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A776" s="3" t="s">
         <v>2395</v>
       </c>
@@ -82424,7 +82424,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="777" spans="1:30">
+    <row r="777" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A777" s="3" t="s">
         <v>2398</v>
       </c>
@@ -82519,7 +82519,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="778" spans="1:30">
+    <row r="778" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A778" s="3" t="s">
         <v>2401</v>
       </c>
@@ -82614,7 +82614,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="779" spans="1:30">
+    <row r="779" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A779" s="3" t="s">
         <v>2404</v>
       </c>
@@ -82709,7 +82709,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="780" spans="1:30">
+    <row r="780" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A780" s="3" t="s">
         <v>2407</v>
       </c>
@@ -82804,7 +82804,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="781" spans="1:30">
+    <row r="781" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A781" s="3" t="s">
         <v>2410</v>
       </c>
@@ -82899,7 +82899,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="782" spans="1:30">
+    <row r="782" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A782" s="3" t="s">
         <v>2413</v>
       </c>
@@ -82994,7 +82994,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="783" spans="1:30">
+    <row r="783" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A783" s="3" t="s">
         <v>2416</v>
       </c>
@@ -83089,7 +83089,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="784" spans="1:30">
+    <row r="784" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A784" s="3" t="s">
         <v>2419</v>
       </c>
@@ -83184,7 +83184,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="785" spans="1:30">
+    <row r="785" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A785" s="3" t="s">
         <v>2422</v>
       </c>
@@ -83279,7 +83279,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="786" spans="1:30">
+    <row r="786" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A786" s="3" t="s">
         <v>2425</v>
       </c>
@@ -83374,7 +83374,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="787" spans="1:30">
+    <row r="787" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A787" s="3" t="s">
         <v>2428</v>
       </c>
@@ -83469,7 +83469,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="788" spans="1:30">
+    <row r="788" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A788" s="3" t="s">
         <v>2431</v>
       </c>
@@ -83564,7 +83564,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="789" spans="1:30">
+    <row r="789" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A789" s="3" t="s">
         <v>2434</v>
       </c>
@@ -83659,7 +83659,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="790" spans="1:30">
+    <row r="790" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A790" s="3" t="s">
         <v>2437</v>
       </c>
@@ -83754,7 +83754,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="791" spans="1:30">
+    <row r="791" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A791" s="3" t="s">
         <v>2440</v>
       </c>
@@ -83849,7 +83849,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="792" spans="1:30">
+    <row r="792" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A792" s="3" t="s">
         <v>2443</v>
       </c>
@@ -83944,7 +83944,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="793" spans="1:30">
+    <row r="793" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A793" s="3" t="s">
         <v>2446</v>
       </c>
@@ -84039,7 +84039,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="794" spans="1:30">
+    <row r="794" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A794" s="3" t="s">
         <v>2449</v>
       </c>
@@ -84134,7 +84134,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="795" spans="1:30">
+    <row r="795" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A795" s="3" t="s">
         <v>2452</v>
       </c>
@@ -84229,7 +84229,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="796" spans="1:30">
+    <row r="796" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A796" s="3" t="s">
         <v>2455</v>
       </c>
@@ -84324,7 +84324,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="797" spans="1:30">
+    <row r="797" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A797" s="3" t="s">
         <v>2458</v>
       </c>
@@ -84419,7 +84419,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="798" spans="1:30">
+    <row r="798" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A798" s="3" t="s">
         <v>2461</v>
       </c>
@@ -84514,7 +84514,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="799" spans="1:30">
+    <row r="799" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A799" s="3" t="s">
         <v>2464</v>
       </c>
@@ -84609,7 +84609,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="800" spans="1:30">
+    <row r="800" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A800" s="3" t="s">
         <v>2467</v>
       </c>
@@ -84704,7 +84704,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="801" spans="1:30">
+    <row r="801" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A801" s="3" t="s">
         <v>2470</v>
       </c>
@@ -84799,7 +84799,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="802" spans="1:30">
+    <row r="802" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A802" s="3" t="s">
         <v>2473</v>
       </c>
@@ -84894,7 +84894,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="803" spans="1:30">
+    <row r="803" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A803" s="3" t="s">
         <v>2476</v>
       </c>
@@ -84989,7 +84989,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="804" spans="1:30">
+    <row r="804" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A804" s="3" t="s">
         <v>2479</v>
       </c>
@@ -85084,7 +85084,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="805" spans="1:30">
+    <row r="805" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A805" s="3" t="s">
         <v>2482</v>
       </c>
@@ -85179,7 +85179,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="806" spans="1:30">
+    <row r="806" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A806" s="3" t="s">
         <v>2485</v>
       </c>
@@ -85274,7 +85274,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="807" spans="1:30">
+    <row r="807" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A807" s="3" t="s">
         <v>2488</v>
       </c>
@@ -85369,7 +85369,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="808" spans="1:30">
+    <row r="808" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A808" s="3" t="s">
         <v>2490</v>
       </c>
@@ -85464,7 +85464,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="809" spans="1:30">
+    <row r="809" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A809" s="3" t="s">
         <v>2493</v>
       </c>
@@ -85559,7 +85559,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="810" spans="1:30">
+    <row r="810" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A810" s="3" t="s">
         <v>2496</v>
       </c>
@@ -85654,7 +85654,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="811" spans="1:30">
+    <row r="811" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A811" s="3" t="s">
         <v>2499</v>
       </c>
@@ -85749,7 +85749,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="812" spans="1:30">
+    <row r="812" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A812" s="3" t="s">
         <v>2502</v>
       </c>
@@ -85844,7 +85844,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="813" spans="1:30">
+    <row r="813" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A813" s="3" t="s">
         <v>2504</v>
       </c>
@@ -85939,7 +85939,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="814" spans="1:30">
+    <row r="814" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A814" s="3" t="s">
         <v>2507</v>
       </c>
@@ -86034,7 +86034,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="815" spans="1:30">
+    <row r="815" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A815" s="3" t="s">
         <v>2510</v>
       </c>
@@ -86129,7 +86129,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="816" spans="1:30">
+    <row r="816" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A816" s="3" t="s">
         <v>2512</v>
       </c>
@@ -86224,7 +86224,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="817" spans="1:30">
+    <row r="817" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A817" s="3" t="s">
         <v>2515</v>
       </c>
@@ -86319,7 +86319,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="818" spans="1:30">
+    <row r="818" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A818" s="3" t="s">
         <v>2518</v>
       </c>
@@ -86414,7 +86414,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="819" spans="1:30">
+    <row r="819" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A819" s="3" t="s">
         <v>2521</v>
       </c>
@@ -86509,7 +86509,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="820" spans="1:30">
+    <row r="820" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A820" s="3" t="s">
         <v>2524</v>
       </c>
@@ -86604,7 +86604,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="821" spans="1:30">
+    <row r="821" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A821" s="3" t="s">
         <v>2527</v>
       </c>
@@ -86699,7 +86699,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="822" spans="1:30">
+    <row r="822" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A822" s="3" t="s">
         <v>2530</v>
       </c>
@@ -86794,7 +86794,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="823" spans="1:30">
+    <row r="823" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A823" s="3" t="s">
         <v>2533</v>
       </c>
@@ -86889,7 +86889,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="824" spans="1:30">
+    <row r="824" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A824" s="3" t="s">
         <v>2536</v>
       </c>
@@ -86984,7 +86984,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="825" spans="1:30">
+    <row r="825" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A825" s="3" t="s">
         <v>2539</v>
       </c>
@@ -87079,7 +87079,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="826" spans="1:30">
+    <row r="826" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A826" s="3" t="s">
         <v>2542</v>
       </c>
@@ -87174,7 +87174,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="827" spans="1:30">
+    <row r="827" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A827" s="3" t="s">
         <v>2545</v>
       </c>
@@ -87269,7 +87269,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="828" spans="1:30">
+    <row r="828" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A828" s="3" t="s">
         <v>2548</v>
       </c>
@@ -87364,7 +87364,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="829" spans="1:30">
+    <row r="829" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A829" s="3" t="s">
         <v>2551</v>
       </c>
@@ -87459,7 +87459,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="830" spans="1:30">
+    <row r="830" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A830" s="3" t="s">
         <v>2554</v>
       </c>
@@ -87554,7 +87554,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="831" spans="1:30">
+    <row r="831" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A831" s="3" t="s">
         <v>2557</v>
       </c>
@@ -87649,7 +87649,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="832" spans="1:30">
+    <row r="832" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A832" s="3" t="s">
         <v>2560</v>
       </c>
@@ -87744,7 +87744,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="833" spans="1:30">
+    <row r="833" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A833" s="3" t="s">
         <v>2563</v>
       </c>
@@ -87839,7 +87839,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="834" spans="1:30">
+    <row r="834" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A834" s="3" t="s">
         <v>2566</v>
       </c>
@@ -87934,7 +87934,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="835" spans="1:30">
+    <row r="835" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A835" s="3" t="s">
         <v>2569</v>
       </c>
@@ -88030,7 +88030,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="836" spans="1:30">
+    <row r="836" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A836" s="3" t="s">
         <v>2572</v>
       </c>
@@ -88125,7 +88125,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="837" spans="1:30">
+    <row r="837" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A837" s="3" t="s">
         <v>2575</v>
       </c>
@@ -88220,7 +88220,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="838" spans="1:30">
+    <row r="838" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A838" s="3" t="s">
         <v>2578</v>
       </c>
@@ -88315,7 +88315,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="839" spans="1:30">
+    <row r="839" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A839" s="3" t="s">
         <v>2581</v>
       </c>
@@ -88410,7 +88410,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="840" spans="1:30">
+    <row r="840" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A840" s="3" t="s">
         <v>2584</v>
       </c>
@@ -88505,7 +88505,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="841" spans="1:30">
+    <row r="841" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A841" s="3" t="s">
         <v>2587</v>
       </c>
@@ -88600,7 +88600,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="842" spans="1:30">
+    <row r="842" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A842" s="3" t="s">
         <v>2590</v>
       </c>
@@ -88695,7 +88695,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="843" spans="1:30">
+    <row r="843" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A843" s="3" t="s">
         <v>2593</v>
       </c>
@@ -88790,7 +88790,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="844" spans="1:30">
+    <row r="844" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A844" s="3" t="s">
         <v>2596</v>
       </c>
@@ -88885,7 +88885,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="845" spans="1:30">
+    <row r="845" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A845" s="3" t="s">
         <v>2599</v>
       </c>
@@ -88980,7 +88980,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="846" spans="1:30">
+    <row r="846" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A846" s="3" t="s">
         <v>2602</v>
       </c>
@@ -89075,7 +89075,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="847" spans="1:30">
+    <row r="847" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A847" s="3" t="s">
         <v>2605</v>
       </c>
@@ -89170,7 +89170,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="848" spans="1:30">
+    <row r="848" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A848" s="3" t="s">
         <v>2607</v>
       </c>
@@ -89265,7 +89265,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="849" spans="1:30">
+    <row r="849" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A849" s="3" t="s">
         <v>2610</v>
       </c>
@@ -89360,7 +89360,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="850" spans="1:30">
+    <row r="850" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A850" s="3" t="s">
         <v>2613</v>
       </c>
@@ -89455,7 +89455,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="851" spans="1:30">
+    <row r="851" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A851" s="3" t="s">
         <v>2616</v>
       </c>
@@ -89550,7 +89550,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="852" spans="1:30">
+    <row r="852" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A852" s="3" t="s">
         <v>2619</v>
       </c>
@@ -89645,7 +89645,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="853" spans="1:30">
+    <row r="853" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A853" s="3" t="s">
         <v>2622</v>
       </c>
@@ -89740,7 +89740,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="854" spans="1:30">
+    <row r="854" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A854" s="3" t="s">
         <v>2625</v>
       </c>
@@ -89835,7 +89835,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="855" spans="1:30">
+    <row r="855" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A855" s="3" t="s">
         <v>2628</v>
       </c>
@@ -89930,7 +89930,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="856" spans="1:30">
+    <row r="856" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A856" s="3" t="s">
         <v>2631</v>
       </c>
@@ -90025,7 +90025,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="857" spans="1:30">
+    <row r="857" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A857" s="3" t="s">
         <v>2634</v>
       </c>
@@ -90120,7 +90120,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="858" spans="1:30">
+    <row r="858" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A858" s="3" t="s">
         <v>2636</v>
       </c>
@@ -90215,7 +90215,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="859" spans="1:30">
+    <row r="859" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A859" s="3" t="s">
         <v>2638</v>
       </c>
@@ -90310,7 +90310,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="860" spans="1:30">
+    <row r="860" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A860" s="3" t="s">
         <v>2640</v>
       </c>
@@ -90405,7 +90405,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="861" spans="1:30">
+    <row r="861" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A861" s="3" t="s">
         <v>2643</v>
       </c>
@@ -90500,7 +90500,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="862" spans="1:30">
+    <row r="862" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A862" s="3" t="s">
         <v>2646</v>
       </c>
@@ -90595,7 +90595,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="863" spans="1:30">
+    <row r="863" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A863" s="3" t="s">
         <v>2649</v>
       </c>
@@ -90690,7 +90690,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="864" spans="1:30">
+    <row r="864" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A864" s="3" t="s">
         <v>2652</v>
       </c>
@@ -90785,7 +90785,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="865" spans="1:30">
+    <row r="865" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A865" s="3" t="s">
         <v>2655</v>
       </c>
@@ -90880,7 +90880,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="866" spans="1:30">
+    <row r="866" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A866" s="3" t="s">
         <v>2658</v>
       </c>
@@ -90975,7 +90975,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="867" spans="1:30">
+    <row r="867" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A867" s="3" t="s">
         <v>2661</v>
       </c>
@@ -91070,7 +91070,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="868" spans="1:30">
+    <row r="868" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A868" s="3" t="s">
         <v>2664</v>
       </c>
@@ -91165,7 +91165,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="869" spans="1:30">
+    <row r="869" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A869" s="3" t="s">
         <v>2667</v>
       </c>
@@ -91260,7 +91260,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="870" spans="1:30">
+    <row r="870" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A870" s="3" t="s">
         <v>2670</v>
       </c>
@@ -91355,7 +91355,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="871" spans="1:30">
+    <row r="871" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A871" s="3" t="s">
         <v>2673</v>
       </c>
@@ -91450,7 +91450,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="872" spans="1:30">
+    <row r="872" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A872" s="3" t="s">
         <v>2675</v>
       </c>
@@ -91545,7 +91545,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="873" spans="1:30">
+    <row r="873" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A873" s="3" t="s">
         <v>2678</v>
       </c>
@@ -91640,7 +91640,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="874" spans="1:30">
+    <row r="874" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A874" s="3" t="s">
         <v>2680</v>
       </c>
@@ -91735,7 +91735,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="875" spans="1:30">
+    <row r="875" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A875" s="3" t="s">
         <v>2682</v>
       </c>
@@ -91830,7 +91830,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="876" spans="1:30">
+    <row r="876" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A876" s="3" t="s">
         <v>2685</v>
       </c>
@@ -91925,7 +91925,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="877" spans="1:30">
+    <row r="877" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A877" s="3" t="s">
         <v>2688</v>
       </c>
@@ -92020,7 +92020,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="878" spans="1:30">
+    <row r="878" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A878" s="3" t="s">
         <v>2691</v>
       </c>
@@ -92115,7 +92115,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="879" spans="1:30">
+    <row r="879" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A879" s="3" t="s">
         <v>2693</v>
       </c>
@@ -92210,7 +92210,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="880" spans="1:30">
+    <row r="880" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A880" s="3" t="s">
         <v>2696</v>
       </c>
@@ -92305,7 +92305,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="881" spans="1:30">
+    <row r="881" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A881" s="3" t="s">
         <v>2699</v>
       </c>
@@ -92400,7 +92400,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="882" spans="1:30">
+    <row r="882" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A882" s="3" t="s">
         <v>2702</v>
       </c>
@@ -92495,7 +92495,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="883" spans="1:30">
+    <row r="883" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A883" s="3" t="s">
         <v>2705</v>
       </c>
@@ -92590,7 +92590,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="884" spans="1:30">
+    <row r="884" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A884" s="3" t="s">
         <v>2708</v>
       </c>
@@ -92685,7 +92685,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="885" spans="1:30">
+    <row r="885" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A885" s="3" t="s">
         <v>2711</v>
       </c>
@@ -92780,7 +92780,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="886" spans="1:30">
+    <row r="886" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A886" s="3" t="s">
         <v>2714</v>
       </c>
@@ -92875,7 +92875,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="887" spans="1:30">
+    <row r="887" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A887" s="3" t="s">
         <v>2717</v>
       </c>
@@ -92970,7 +92970,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="888" spans="1:30">
+    <row r="888" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A888" s="3" t="s">
         <v>2720</v>
       </c>
@@ -93065,7 +93065,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="889" spans="1:30">
+    <row r="889" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A889" s="3" t="s">
         <v>2723</v>
       </c>
@@ -93160,7 +93160,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="890" spans="1:30">
+    <row r="890" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A890" s="3" t="s">
         <v>2726</v>
       </c>
@@ -93255,7 +93255,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="891" spans="1:30">
+    <row r="891" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A891" s="3" t="s">
         <v>2729</v>
       </c>
@@ -93350,7 +93350,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="892" spans="1:30">
+    <row r="892" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A892" s="3" t="s">
         <v>2731</v>
       </c>
@@ -93445,7 +93445,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="893" spans="1:30">
+    <row r="893" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A893" s="3" t="s">
         <v>2734</v>
       </c>
@@ -93540,7 +93540,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="894" spans="1:30">
+    <row r="894" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A894" s="3" t="s">
         <v>2737</v>
       </c>
@@ -93635,7 +93635,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="895" spans="1:30">
+    <row r="895" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A895" s="3" t="s">
         <v>2740</v>
       </c>
@@ -93730,7 +93730,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="896" spans="1:30">
+    <row r="896" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A896" s="3" t="s">
         <v>2743</v>
       </c>
@@ -93825,7 +93825,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="897" spans="1:30">
+    <row r="897" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A897" s="3" t="s">
         <v>2746</v>
       </c>
@@ -93920,7 +93920,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="898" spans="1:30">
+    <row r="898" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A898" s="3" t="s">
         <v>2749</v>
       </c>
@@ -94015,7 +94015,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="899" spans="1:30">
+    <row r="899" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A899" s="3" t="s">
         <v>2752</v>
       </c>
@@ -94111,7 +94111,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="900" spans="1:30">
+    <row r="900" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A900" s="3" t="s">
         <v>2754</v>
       </c>
@@ -94206,7 +94206,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="901" spans="1:30">
+    <row r="901" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A901" s="3" t="s">
         <v>2757</v>
       </c>
@@ -94301,7 +94301,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="902" spans="1:30">
+    <row r="902" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A902" s="3" t="s">
         <v>1096</v>
       </c>
@@ -94396,7 +94396,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="903" spans="1:30">
+    <row r="903" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A903" s="3" t="s">
         <v>380</v>
       </c>
@@ -94491,7 +94491,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="904" spans="1:30">
+    <row r="904" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A904" s="3" t="s">
         <v>1220</v>
       </c>
@@ -94586,7 +94586,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="905" spans="1:30">
+    <row r="905" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A905" s="3" t="s">
         <v>778</v>
       </c>
@@ -94681,7 +94681,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="906" spans="1:30">
+    <row r="906" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A906" s="3" t="s">
         <v>1046</v>
       </c>
@@ -94776,7 +94776,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="907" spans="1:30">
+    <row r="907" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A907" s="3" t="s">
         <v>618</v>
       </c>
@@ -94871,7 +94871,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="908" spans="1:30">
+    <row r="908" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A908" s="3" t="s">
         <v>1369</v>
       </c>
@@ -94966,7 +94966,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="909" spans="1:30">
+    <row r="909" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A909" s="3" t="s">
         <v>1807</v>
       </c>
@@ -95061,7 +95061,7 @@
         <v>Warning</v>
       </c>
     </row>
-    <row r="910" spans="1:30">
+    <row r="910" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A910" s="3" t="s">
         <v>535</v>
       </c>
@@ -95156,7 +95156,7 @@
         <v>Invalid</v>
       </c>
     </row>
-    <row r="911" spans="1:30">
+    <row r="911" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A911" s="3" t="s">
         <v>921</v>
       </c>
@@ -95251,7 +95251,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="912" spans="1:30">
+    <row r="912" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A912" s="3" t="s">
         <v>478</v>
       </c>
@@ -95346,7 +95346,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="913" spans="1:30">
+    <row r="913" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A913" s="3" t="s">
         <v>1108</v>
       </c>
@@ -95441,7 +95441,7 @@
         <v>Clean</v>
       </c>
     </row>
-    <row r="914" spans="1:30">
+    <row r="914" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C914" s="8"/>
       <c r="D914" s="4"/>
       <c r="E914"/>
@@ -95452,7 +95452,7 @@
       <c r="X914" s="4"/>
       <c r="Y914" s="4"/>
     </row>
-    <row r="915" spans="1:30">
+    <row r="915" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C915" s="8"/>
       <c r="D915" s="4"/>
       <c r="E915"/>
@@ -95463,7 +95463,7 @@
       <c r="X915" s="4"/>
       <c r="Y915" s="4"/>
     </row>
-    <row r="916" spans="1:30">
+    <row r="916" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C916" s="8"/>
       <c r="D916" s="4"/>
       <c r="E916"/>
@@ -95474,7 +95474,7 @@
       <c r="X916" s="4"/>
       <c r="Y916" s="4"/>
     </row>
-    <row r="917" spans="1:30">
+    <row r="917" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C917" s="8"/>
       <c r="D917" s="4"/>
       <c r="E917"/>
@@ -95485,7 +95485,7 @@
       <c r="X917" s="4"/>
       <c r="Y917" s="4"/>
     </row>
-    <row r="918" spans="1:30">
+    <row r="918" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C918" s="8"/>
       <c r="D918" s="4"/>
       <c r="E918"/>
@@ -95496,7 +95496,7 @@
       <c r="X918" s="4"/>
       <c r="Y918" s="4"/>
     </row>
-    <row r="919" spans="1:30">
+    <row r="919" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C919" s="8"/>
       <c r="D919" s="4"/>
       <c r="E919"/>
@@ -95507,7 +95507,7 @@
       <c r="X919" s="4"/>
       <c r="Y919" s="4"/>
     </row>
-    <row r="920" spans="1:30">
+    <row r="920" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C920" s="8"/>
       <c r="D920" s="4"/>
       <c r="E920"/>
@@ -95518,7 +95518,7 @@
       <c r="X920" s="4"/>
       <c r="Y920" s="4"/>
     </row>
-    <row r="921" spans="1:30">
+    <row r="921" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C921" s="8"/>
       <c r="D921" s="4"/>
       <c r="E921"/>
@@ -95529,7 +95529,7 @@
       <c r="X921" s="4"/>
       <c r="Y921" s="4"/>
     </row>
-    <row r="922" spans="1:30">
+    <row r="922" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C922" s="8"/>
       <c r="D922" s="4"/>
       <c r="E922"/>
@@ -95540,7 +95540,7 @@
       <c r="X922" s="4"/>
       <c r="Y922" s="4"/>
     </row>
-    <row r="923" spans="1:30">
+    <row r="923" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C923" s="8"/>
       <c r="D923" s="4"/>
       <c r="E923"/>
@@ -95551,7 +95551,7 @@
       <c r="X923" s="4"/>
       <c r="Y923" s="4"/>
     </row>
-    <row r="924" spans="1:30">
+    <row r="924" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C924" s="8"/>
       <c r="D924" s="4"/>
       <c r="E924"/>
@@ -95562,7 +95562,7 @@
       <c r="X924" s="4"/>
       <c r="Y924" s="4"/>
     </row>
-    <row r="925" spans="1:30">
+    <row r="925" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C925" s="8"/>
       <c r="D925" s="4"/>
       <c r="E925"/>
@@ -95573,7 +95573,7 @@
       <c r="X925" s="4"/>
       <c r="Y925" s="4"/>
     </row>
-    <row r="926" spans="1:30">
+    <row r="926" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C926" s="8"/>
       <c r="D926" s="4"/>
       <c r="E926"/>
@@ -95584,7 +95584,7 @@
       <c r="X926" s="4"/>
       <c r="Y926" s="4"/>
     </row>
-    <row r="927" spans="1:30">
+    <row r="927" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C927" s="8"/>
       <c r="D927" s="4"/>
       <c r="E927"/>
@@ -95595,7 +95595,7 @@
       <c r="X927" s="4"/>
       <c r="Y927" s="4"/>
     </row>
-    <row r="928" spans="1:30">
+    <row r="928" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C928" s="8"/>
       <c r="D928" s="4"/>
       <c r="E928"/>
@@ -95606,7 +95606,7 @@
       <c r="X928" s="4"/>
       <c r="Y928" s="4"/>
     </row>
-    <row r="929" spans="3:25">
+    <row r="929" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C929" s="8"/>
       <c r="D929" s="4"/>
       <c r="E929"/>
@@ -95617,7 +95617,7 @@
       <c r="X929" s="4"/>
       <c r="Y929" s="4"/>
     </row>
-    <row r="930" spans="3:25">
+    <row r="930" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C930" s="8"/>
       <c r="D930" s="4"/>
       <c r="E930"/>
@@ -95628,7 +95628,7 @@
       <c r="X930" s="4"/>
       <c r="Y930" s="4"/>
     </row>
-    <row r="931" spans="3:25">
+    <row r="931" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C931" s="8"/>
       <c r="D931" s="4"/>
       <c r="E931"/>
@@ -95639,7 +95639,7 @@
       <c r="X931" s="4"/>
       <c r="Y931" s="4"/>
     </row>
-    <row r="932" spans="3:25">
+    <row r="932" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C932" s="8"/>
       <c r="D932" s="4"/>
       <c r="E932"/>
@@ -95650,7 +95650,7 @@
       <c r="X932" s="4"/>
       <c r="Y932" s="4"/>
     </row>
-    <row r="933" spans="3:25">
+    <row r="933" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C933" s="8"/>
       <c r="D933" s="4"/>
       <c r="E933"/>
@@ -95670,12 +95670,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="27.95" customHeight="1">
+    <row r="1" spans="1:2" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2760</v>
       </c>
@@ -95683,7 +95683,7 @@
         <v>2761</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="42.75">
+    <row r="2" spans="1:2" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>2762</v>
       </c>
@@ -95691,7 +95691,7 @@
         <v>2763</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="28.5">
+    <row r="3" spans="1:2" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>2764</v>
       </c>
@@ -95699,7 +95699,7 @@
         <v>2765</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="28.5">
+    <row r="4" spans="1:2" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>2766</v>
       </c>
@@ -95707,7 +95707,7 @@
         <v>2765</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="28.5">
+    <row r="5" spans="1:2" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>2767</v>
       </c>
@@ -95715,7 +95715,7 @@
         <v>2768</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="42.75">
+    <row r="6" spans="1:2" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>2769</v>
       </c>
@@ -95723,7 +95723,7 @@
         <v>2770</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="57">
+    <row r="7" spans="1:2" ht="57" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>2771</v>
       </c>
@@ -95731,7 +95731,7 @@
         <v>2772</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="28.5">
+    <row r="8" spans="1:2" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>2773</v>
       </c>
@@ -95739,7 +95739,7 @@
         <v>2774</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="42.75">
+    <row r="9" spans="1:2" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>2775</v>
       </c>
@@ -95747,7 +95747,7 @@
         <v>2776</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="71.25">
+    <row r="10" spans="1:2" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>2777</v>
       </c>
@@ -95755,7 +95755,7 @@
         <v>2778</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="42.75">
+    <row r="11" spans="1:2" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>2779</v>
       </c>
